--- a/tables/N-Retention/Local_estpar_protection_False_vo_False_CUE_True.xlsx
+++ b/tables/N-Retention/Local_estpar_protection_False_vo_False_CUE_True.xlsx
@@ -573,61 +573,61 @@
         <v>70.85714285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.432164952517398</v>
+        <v>0.4321649524844555</v>
       </c>
       <c r="G2" t="n">
         <v>0.04480286738351254</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2627803891781534</v>
+        <v>0.2627803892434106</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2428872347095719</v>
+        <v>0.2428872346838566</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01736455621136393</v>
+        <v>0.01736455620476475</v>
       </c>
       <c r="K2" t="n">
-        <v>0.231221768074665</v>
+        <v>0.1686476518040546</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2007269617388088</v>
+        <v>0.1781455615383475</v>
       </c>
       <c r="M2" t="n">
-        <v>4.423003063843023</v>
+        <v>4.417326970572913</v>
       </c>
       <c r="N2" t="n">
-        <v>4.425653982279559</v>
+        <v>4.423670708723406</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001036032006088106</v>
+        <v>0.0009757843295375942</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0009662827570444669</v>
+        <v>0.0008865517833964531</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.000735489231872479</v>
+        <v>0.0007252836281064477</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001000328031070554</v>
+        <v>0.0009150038277617531</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0006280709248107305</v>
+        <v>0.0005617456383050052</v>
       </c>
       <c r="T2" t="n">
-        <v>0.002145777576437048</v>
+        <v>0.002054808524816001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002469230473450296</v>
+        <v>0.002259388756999977</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001686670409332393</v>
+        <v>0.001659504320642964</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001952011779021637</v>
+        <v>0.00186113758361474</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001484373810011251</v>
+        <v>0.001389695724625419</v>
       </c>
     </row>
     <row r="3">
@@ -653,61 +653,61 @@
         <v>82.71186440677965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4230480283044928</v>
+        <v>0.4230480283479805</v>
       </c>
       <c r="G3" t="n">
         <v>0.03838147280770231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3417824749441816</v>
+        <v>0.341782474747073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733633998846752</v>
+        <v>0.1733633999809309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02342462405894816</v>
+        <v>0.02342462411631339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1244613220022463</v>
+        <v>0.07314718350049879</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5532317643366048</v>
+        <v>0.5527755962422467</v>
       </c>
       <c r="M3" t="n">
-        <v>4.380933480146111</v>
+        <v>4.380918698941214</v>
       </c>
       <c r="N3" t="n">
-        <v>4.404242350358435</v>
+        <v>4.402754024057271</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001257327964236741</v>
+        <v>0.001238003151174383</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001529352293956586</v>
+        <v>0.001507365457874455</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4999999999997544</v>
+        <v>0.4999999999966007</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001549393302261924</v>
+        <v>0.001505094663222991</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009746554421226075</v>
+        <v>0.0009447518000606671</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002600062950760285</v>
+        <v>0.002604786784344995</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002469884541004454</v>
+        <v>0.002482092439082843</v>
       </c>
       <c r="V3" t="n">
-        <v>615.0133466702283</v>
+        <v>491.2344649708722</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002892383052738369</v>
+        <v>0.002946957840574382</v>
       </c>
       <c r="X3" t="n">
-        <v>0.002261639854574159</v>
+        <v>0.002262457573966016</v>
       </c>
     </row>
     <row r="4">
@@ -733,61 +733,61 @@
         <v>38.828125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5026131523004256</v>
+        <v>0.5026131523545405</v>
       </c>
       <c r="G4" t="n">
         <v>0.08176040369199321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1418117772088146</v>
+        <v>0.1418117771640022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2720282171617107</v>
+        <v>0.2720282171735377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001786449637055907</v>
+        <v>0.00178644961592619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4279806051287939</v>
+        <v>0.3914415207441552</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2200848300617113</v>
+        <v>0.280142845372039</v>
       </c>
       <c r="M4" t="n">
-        <v>4.387539913380152</v>
+        <v>4.396872801486738</v>
       </c>
       <c r="N4" t="n">
-        <v>4.498711017284148</v>
+        <v>4.489813794909869</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001645559458103736</v>
+        <v>0.001515204594416444</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0008087354830248767</v>
+        <v>0.0009038949884358358</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0003294824558096251</v>
+        <v>0.0003380010415343629</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001189542491021514</v>
+        <v>0.001153314842365964</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0003124082131838928</v>
+        <v>0.0003532644896695644</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003977752638963215</v>
+        <v>0.003585840778413283</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001786552053333507</v>
+        <v>0.001929181955663625</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001348230074555648</v>
+        <v>0.001376577590528016</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002198009554598652</v>
+        <v>0.002220116490846985</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001672230722055263</v>
+        <v>0.001866752497990288</v>
       </c>
     </row>
     <row r="5">
@@ -813,61 +813,61 @@
         <v>67.8082191780822</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4142260612899763</v>
+        <v>0.414226061397911</v>
       </c>
       <c r="G5" t="n">
         <v>0.04681738015071348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2912830177383198</v>
+        <v>0.2912830175544637</v>
       </c>
       <c r="I5" t="n">
-        <v>0.217379291417003</v>
+        <v>0.2173792914645093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03029424940398749</v>
+        <v>0.03029424943240262</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1827280885331473</v>
+        <v>0.1240122399021428</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2173228672351335</v>
+        <v>0.1729422347957283</v>
       </c>
       <c r="M5" t="n">
-        <v>4.284288827803178</v>
+        <v>4.2780063223785</v>
       </c>
       <c r="N5" t="n">
-        <v>4.352741668080514</v>
+        <v>4.344036163884674</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0009242445963564818</v>
+        <v>0.0008924122775865183</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0008760183125182416</v>
+        <v>0.0007472713295204301</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0008332629263514857</v>
+        <v>0.0008113331554568344</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0008223898332369852</v>
+        <v>0.0007439715887148467</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001143065922391305</v>
+        <v>0.001043176879702062</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001884644665558544</v>
+        <v>0.001855351872599346</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002341352148472269</v>
+        <v>0.002033784771199951</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00192061831999119</v>
+        <v>0.001866587074529943</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001614348011847374</v>
+        <v>0.001510327589497833</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002417923830234358</v>
+        <v>0.002243358430321384</v>
       </c>
     </row>
     <row r="6">
@@ -893,61 +893,61 @@
         <v>77.65625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3890909284533883</v>
+        <v>0.3890909284112034</v>
       </c>
       <c r="G6" t="n">
         <v>0.0408802018459966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3036991224550851</v>
+        <v>0.3036991225960292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2478250703308909</v>
+        <v>0.2478250702399798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01850467691463906</v>
+        <v>0.01850467690679097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1686949492158193</v>
+        <v>0.1119319167897971</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2031631611608511</v>
+        <v>0.5576191286288669</v>
       </c>
       <c r="M6" t="n">
-        <v>4.342240460276607</v>
+        <v>4.380999399795989</v>
       </c>
       <c r="N6" t="n">
-        <v>4.389825710690048</v>
+        <v>4.437378525376107</v>
       </c>
       <c r="O6" t="n">
-        <v>0.000651312701006058</v>
+        <v>0.001027813908255815</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0005099155811175804</v>
+        <v>0.001496146553348829</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0005364072539135407</v>
+        <v>0.4948646687757194</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003908353250329754</v>
+        <v>0.0009015816208641667</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003406956289848433</v>
+        <v>0.001053073722726463</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001340625469999828</v>
+        <v>0.001993120961303644</v>
       </c>
       <c r="U6" t="n">
-        <v>0.00127736737723554</v>
+        <v>0.005878754987411021</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001238685418166805</v>
+        <v>699.1048263503578</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0009599132045563177</v>
+        <v>0.002036870238337622</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001003736410067644</v>
+        <v>0.002439937528636854</v>
       </c>
     </row>
     <row r="7">
@@ -973,61 +973,61 @@
         <v>66.19718309859155</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4886958146778536</v>
+        <v>0.4886958146760266</v>
       </c>
       <c r="G7" t="n">
         <v>0.04795677136102667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2566075839924613</v>
+        <v>0.2566075840123206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1893475641758934</v>
+        <v>0.1893475641544703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01739226579276497</v>
+        <v>0.01739226579615577</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2352928704016582</v>
+        <v>0.1767282951938061</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1604853992140176</v>
+        <v>0.5531199154780186</v>
       </c>
       <c r="M7" t="n">
-        <v>4.326727858682707</v>
+        <v>4.381466282293213</v>
       </c>
       <c r="N7" t="n">
-        <v>4.36241420547643</v>
+        <v>4.401460796253241</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001074289968300523</v>
+        <v>0.001923243818236849</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0005365638204445219</v>
+        <v>0.001466061747697633</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0005592155013247618</v>
+        <v>0.4995950455023548</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0009302210774422094</v>
+        <v>0.002547458438093059</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004929164686758991</v>
+        <v>0.001326637173416831</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002359425299703345</v>
+        <v>0.004268992704731009</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001447297907551995</v>
+        <v>0.002640069735121978</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001315483205933259</v>
+        <v>637.1527004512047</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001748756675784782</v>
+        <v>0.004847603160949917</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001832855044662307</v>
+        <v>0.003568288643038036</v>
       </c>
     </row>
     <row r="8">
@@ -1053,61 +1053,61 @@
         <v>66.66666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3735503885622976</v>
+        <v>0.3735503886646729</v>
       </c>
       <c r="G8" t="n">
         <v>0.04761904761904761</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3017797553926043</v>
+        <v>0.3017797550644881</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2489905948482005</v>
+        <v>0.2489905949934041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02806021357785015</v>
+        <v>0.02806021365838738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1764617114806127</v>
+        <v>0.1163738186416686</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1677748955293183</v>
+        <v>0.1370752768277862</v>
       </c>
       <c r="M8" t="n">
-        <v>4.467111511766626</v>
+        <v>4.45907317773111</v>
       </c>
       <c r="N8" t="n">
-        <v>4.408446806959899</v>
+        <v>4.410279949780879</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001418960387401615</v>
+        <v>0.00139326853827299</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0007978216943776737</v>
+        <v>0.0007068392993439681</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001079853749075233</v>
+        <v>0.001029354026564272</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001453416055765939</v>
+        <v>0.001354700446649457</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0007051272088324261</v>
+        <v>0.0006341741099555358</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003222803367381256</v>
+        <v>0.003246264457124465</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002439329016479102</v>
+        <v>0.001894651324188482</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002623741165215543</v>
+        <v>0.002479165377554438</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003124480053406773</v>
+        <v>0.003001408484346012</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001497695012936784</v>
+        <v>0.001319619047877632</v>
       </c>
     </row>
     <row r="9">
@@ -1133,61 +1133,61 @@
         <v>69.85074626865672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4184346509008527</v>
+        <v>0.4184346509642805</v>
       </c>
       <c r="G9" t="n">
         <v>0.0454483787817121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2664295170187482</v>
+        <v>0.2664295168783421</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2311091971008347</v>
+        <v>0.2311091971723147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03857825619785213</v>
+        <v>0.03857825620335059</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2172585063083445</v>
+        <v>0.157077219662575</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1624380954410181</v>
+        <v>0.1448930802681667</v>
       </c>
       <c r="M9" t="n">
-        <v>4.269401659677728</v>
+        <v>4.263939619854584</v>
       </c>
       <c r="N9" t="n">
-        <v>4.35874284536439</v>
+        <v>4.351307571260873</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001456047238585764</v>
+        <v>0.001396190446108023</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0007551275670578868</v>
+        <v>0.0007002371161998615</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0007651046818740468</v>
+        <v>0.0007528609604354501</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0009194801609671706</v>
+        <v>0.0008520337593878864</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0008209180541740575</v>
+        <v>0.0007742157769828549</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003402740516646168</v>
+        <v>0.003281944893748909</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002006685839544211</v>
+        <v>0.001665410324090522</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001754789781239157</v>
+        <v>0.001716313556925713</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001758212368149434</v>
+        <v>0.001711095236283874</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001639551999818251</v>
+        <v>0.001578002386321104</v>
       </c>
     </row>
     <row r="10">
@@ -1213,61 +1213,61 @@
         <v>52.61363636363636</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5306916825504616</v>
+        <v>0.5306916826579526</v>
       </c>
       <c r="G10" t="n">
         <v>0.0603380301004491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2597511503162143</v>
+        <v>0.2597511501438604</v>
       </c>
       <c r="I10" t="n">
-        <v>0.115376694226804</v>
+        <v>0.1153766942703101</v>
       </c>
       <c r="J10" t="n">
-        <v>0.033842442806071</v>
+        <v>0.03384244282742767</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2218064918079044</v>
+        <v>0.1626744397818159</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1173399458770293</v>
+        <v>0.1115453676071589</v>
       </c>
       <c r="M10" t="n">
-        <v>4.174011962406782</v>
+        <v>4.162069851699079</v>
       </c>
       <c r="N10" t="n">
-        <v>4.218924371192989</v>
+        <v>4.209610717156572</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001259192677129684</v>
+        <v>0.001235717698128728</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0006612739729162408</v>
+        <v>0.0006323166699016608</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0005632700590013608</v>
+        <v>0.0005520964227483791</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001058317475660811</v>
+        <v>0.0009486106192685882</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0005964774884366355</v>
+        <v>0.0005690182364600971</v>
       </c>
       <c r="T10" t="n">
-        <v>0.002863076604985887</v>
+        <v>0.002870530964359709</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001487224594352429</v>
+        <v>0.001441195671326378</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001322481297581944</v>
+        <v>0.001297196854055959</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001971689920623121</v>
+        <v>0.001844612700589079</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001309170985461035</v>
+        <v>0.001304231354195471</v>
       </c>
     </row>
     <row r="11">
@@ -1293,61 +1293,61 @@
         <v>61.69014084507042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6976459379986636</v>
+        <v>0.6976459379735106</v>
       </c>
       <c r="G11" t="n">
         <v>0.05146046241936653</v>
       </c>
       <c r="H11" t="n">
-        <v>0.128689928922737</v>
+        <v>0.1286899289623047</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09261029160041566</v>
+        <v>0.09261029157801856</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02959337905881725</v>
+        <v>0.02959337906679948</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4207296396380543</v>
+        <v>0.3893680180148595</v>
       </c>
       <c r="L11" t="n">
-        <v>0.412912623367632</v>
+        <v>0.4303467575663382</v>
       </c>
       <c r="M11" t="n">
-        <v>4.138303272798723</v>
+        <v>4.130128332940494</v>
       </c>
       <c r="N11" t="n">
-        <v>4.27316255191388</v>
+        <v>4.278045065566874</v>
       </c>
       <c r="O11" t="n">
-        <v>0.001673900131450211</v>
+        <v>0.001782423528081741</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001594204364284838</v>
+        <v>0.001688545476485404</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001490841560342167</v>
+        <v>0.001420784704361047</v>
       </c>
       <c r="R11" t="n">
-        <v>0.002640731240849343</v>
+        <v>0.002608905308762669</v>
       </c>
       <c r="S11" t="n">
-        <v>0.002119465318431114</v>
+        <v>0.002091773511800344</v>
       </c>
       <c r="T11" t="n">
-        <v>0.003643715298626145</v>
+        <v>0.003807658795578871</v>
       </c>
       <c r="U11" t="n">
-        <v>0.004016522083663568</v>
+        <v>0.004552275731262917</v>
       </c>
       <c r="V11" t="n">
-        <v>0.003499101599421179</v>
+        <v>0.003403526930444082</v>
       </c>
       <c r="W11" t="n">
-        <v>0.004020080134975325</v>
+        <v>0.004428824633662782</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0039324630115234</v>
+        <v>0.00398338560280851</v>
       </c>
     </row>
     <row r="12">
@@ -1373,61 +1373,61 @@
         <v>1182.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6580079528637066</v>
+        <v>0.658007952809377</v>
       </c>
       <c r="G12" t="n">
         <v>0.002684653847444545</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3185832282923884</v>
+        <v>0.3185832283714021</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0207241649964606</v>
+        <v>0.02072416497177636</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1391705992174257</v>
+        <v>0.09114342333800676</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1300375764170898</v>
+        <v>0.4479008347671788</v>
       </c>
       <c r="M12" t="n">
-        <v>4.050355388189223</v>
+        <v>4.199227117020402</v>
       </c>
       <c r="N12" t="n">
-        <v>4.107311319387667</v>
+        <v>4.258648214890808</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0006223773152476979</v>
+        <v>0.0004848171731846285</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0003433074258398214</v>
+        <v>0.002583695658130197</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0005049849344003327</v>
+        <v>0.002310116762644658</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001186532084941266</v>
+        <v>0.005130991500015739</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0005140190904057066</v>
+        <v>0.001034738069581559</v>
       </c>
       <c r="T12" t="n">
-        <v>0.001329141422415126</v>
+        <v>0.001193310720375647</v>
       </c>
       <c r="U12" t="n">
-        <v>0.003136605458401972</v>
+        <v>0.003381274238011428</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001164153273827559</v>
+        <v>0.005052394952270832</v>
       </c>
       <c r="W12" t="n">
-        <v>0.005506527501170613</v>
+        <v>0.009286538921415032</v>
       </c>
       <c r="X12" t="n">
-        <v>0.001082203260536435</v>
+        <v>0.001691713119461504</v>
       </c>
     </row>
     <row r="13">
@@ -1453,61 +1453,61 @@
         <v>37.30769230769231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3764292995365501</v>
+        <v>0.3764292995885038</v>
       </c>
       <c r="G13" t="n">
         <v>0.08509245622647683</v>
       </c>
       <c r="H13" t="n">
-        <v>0.20530781079537</v>
+        <v>0.2053078106416003</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2773838130683605</v>
+        <v>0.2773838131849478</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05578662037324268</v>
+        <v>0.0557866203584713</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3163103270805452</v>
+        <v>0.2606845114519389</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2744156818244717</v>
+        <v>0.2330219432619249</v>
       </c>
       <c r="M13" t="n">
-        <v>4.301008304553289</v>
+        <v>4.29447068677675</v>
       </c>
       <c r="N13" t="n">
-        <v>4.501660482213083</v>
+        <v>4.505896250710505</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001334898086460993</v>
+        <v>0.001181807200045621</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0009867781638271623</v>
+        <v>0.0007811696470927246</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.001072185109332468</v>
+        <v>0.0009877538019573582</v>
       </c>
       <c r="R13" t="n">
-        <v>0.00923391959654158</v>
+        <v>0.008867227404493699</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01539471946977066</v>
+        <v>0.01500937982983679</v>
       </c>
       <c r="T13" t="n">
-        <v>0.006877203343455786</v>
+        <v>0.006556376721509202</v>
       </c>
       <c r="U13" t="n">
-        <v>0.015603066268275</v>
+        <v>0.01386136626969037</v>
       </c>
       <c r="V13" t="n">
-        <v>0.00633224878519378</v>
+        <v>0.006231494279849581</v>
       </c>
       <c r="W13" t="n">
-        <v>0.01766331595694656</v>
+        <v>0.01724549756694927</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03720762474310246</v>
+        <v>0.03633530094254434</v>
       </c>
     </row>
     <row r="14">
@@ -1533,61 +1533,61 @@
         <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4685666630154797</v>
+        <v>0.4685666629631464</v>
       </c>
       <c r="G14" t="n">
         <v>0.07215007215007214</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2791093997172449</v>
+        <v>0.2791093997308827</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1713546933726054</v>
+        <v>0.1713546934252931</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008819171744597891</v>
+        <v>0.008819171730605837</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2032160166229758</v>
+        <v>0.142225613090205</v>
       </c>
       <c r="L14" t="n">
-        <v>0.297416438428291</v>
+        <v>0.2340461287766268</v>
       </c>
       <c r="M14" t="n">
-        <v>4.356050107737354</v>
+        <v>4.346268431100555</v>
       </c>
       <c r="N14" t="n">
-        <v>4.376213624331232</v>
+        <v>4.364949725962516</v>
       </c>
       <c r="O14" t="n">
-        <v>0.00662040981854567</v>
+        <v>0.005986544818102246</v>
       </c>
       <c r="P14" t="n">
-        <v>1.000000000045164e-05</v>
+        <v>0.0003200399795979572</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.008438686354812173</v>
+        <v>0.007803999266660584</v>
       </c>
       <c r="R14" t="n">
-        <v>0.007161484202735454</v>
+        <v>0.00602083083747987</v>
       </c>
       <c r="S14" t="n">
-        <v>0.01088583477710988</v>
+        <v>0.008672518368232324</v>
       </c>
       <c r="T14" t="n">
-        <v>0.09180619141027958</v>
+        <v>0.08779177466414517</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3543577842680267</v>
+        <v>0.3197688315208311</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0176162767620578</v>
+        <v>0.01626329590717245</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01566077659594805</v>
+        <v>0.01464950344690536</v>
       </c>
       <c r="X14" t="n">
-        <v>0.03172426051682783</v>
+        <v>0.02907298019716282</v>
       </c>
     </row>
     <row r="15">
@@ -1613,61 +1613,61 @@
         <v>37.66666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4676168791864762</v>
+        <v>0.467616879374457</v>
       </c>
       <c r="G15" t="n">
         <v>0.08428150021070376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2808036479653256</v>
+        <v>0.280803647842334</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1470517109277883</v>
+        <v>0.1470517108760386</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02024626170970604</v>
+        <v>0.02024626169646662</v>
       </c>
       <c r="K15" t="n">
-        <v>0.18717447583358</v>
+        <v>0.1304836268708661</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2802752231301741</v>
+        <v>0.2250345735371539</v>
       </c>
       <c r="M15" t="n">
-        <v>4.078910665279218</v>
+        <v>4.071216775025594</v>
       </c>
       <c r="N15" t="n">
-        <v>4.255520849975503</v>
+        <v>4.236733696179028</v>
       </c>
       <c r="O15" t="n">
-        <v>0.00607586072160539</v>
+        <v>0.005833434179653676</v>
       </c>
       <c r="P15" t="n">
-        <v>0.002444229941098794</v>
+        <v>0.001718759962112743</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.008014431497273503</v>
+        <v>0.007793192043241314</v>
       </c>
       <c r="R15" t="n">
-        <v>0.005477766760053277</v>
+        <v>0.00452527309090206</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02492501218807375</v>
+        <v>0.02251332072834291</v>
       </c>
       <c r="T15" t="n">
-        <v>0.01187881636543209</v>
+        <v>0.01153415500789025</v>
       </c>
       <c r="U15" t="n">
-        <v>0.008338162958266455</v>
+        <v>0.00767555979538294</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01709898557325353</v>
+        <v>0.01662350054001277</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01170941390785224</v>
+        <v>0.01075584225253598</v>
       </c>
       <c r="X15" t="n">
-        <v>0.08581813255588283</v>
+        <v>0.07552333260644956</v>
       </c>
     </row>
     <row r="16">
@@ -1693,61 +1693,61 @@
         <v>21.39130434782609</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3751087963773801</v>
+        <v>0.3751087964018581</v>
       </c>
       <c r="G16" t="n">
         <v>0.1484062459672215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06809149804835848</v>
+        <v>0.06809149804106746</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3926949046640935</v>
+        <v>0.3926949046425352</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01569855494294647</v>
+        <v>0.01569855494731771</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5236690839066376</v>
+        <v>0.5116905935028913</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5447768992630679</v>
+        <v>0.5582179888756231</v>
       </c>
       <c r="M16" t="n">
-        <v>4.405739545165345</v>
+        <v>4.397292039063695</v>
       </c>
       <c r="N16" t="n">
-        <v>4.588775395438945</v>
+        <v>4.544704064845276</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02629433258354745</v>
+        <v>0.02710443282381944</v>
       </c>
       <c r="P16" t="n">
-        <v>0.01825767335536112</v>
+        <v>0.01899889833695825</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01995705346006832</v>
+        <v>0.02074691719071987</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01271085112942659</v>
+        <v>0.01319821921476901</v>
       </c>
       <c r="S16" t="n">
-        <v>0.001687308682514193</v>
+        <v>0.005372192387672814</v>
       </c>
       <c r="T16" t="n">
-        <v>0.07843503510841023</v>
+        <v>0.2239777452380434</v>
       </c>
       <c r="U16" t="n">
-        <v>0.04261755193331022</v>
+        <v>0.1979543662694198</v>
       </c>
       <c r="V16" t="n">
-        <v>0.05173303355811669</v>
+        <v>0.2233512148783388</v>
       </c>
       <c r="W16" t="n">
-        <v>0.02890125780247119</v>
+        <v>0.1297776657704041</v>
       </c>
       <c r="X16" t="n">
-        <v>11.82870769866166</v>
+        <v>25.43621666171475</v>
       </c>
     </row>
     <row r="17">
@@ -1773,61 +1773,61 @@
         <v>51.25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4780640258980272</v>
+        <v>0.478064025668827</v>
       </c>
       <c r="G17" t="n">
         <v>0.06194347657762291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2550441184335309</v>
+        <v>0.2550441188812936</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1330574186338084</v>
+        <v>0.1330574185135598</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07189096045701066</v>
+        <v>0.07189096035869673</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2115225658269365</v>
+        <v>0.1561989488837014</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2651068195247229</v>
+        <v>0.2088196181295663</v>
       </c>
       <c r="M17" t="n">
-        <v>3.878915072695432</v>
+        <v>3.852813853820157</v>
       </c>
       <c r="N17" t="n">
-        <v>4.037655144363148</v>
+        <v>4.001696627628808</v>
       </c>
       <c r="O17" t="n">
-        <v>0.006557965057989544</v>
+        <v>0.006334073447950004</v>
       </c>
       <c r="P17" t="n">
-        <v>0.001688490954166895</v>
+        <v>0.000906638687091994</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.006678158655676662</v>
+        <v>0.006530328641540274</v>
       </c>
       <c r="R17" t="n">
-        <v>0.004552909902029429</v>
+        <v>0.003586959468513591</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01067011072874225</v>
+        <v>0.0102591741582876</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01270806875897575</v>
+        <v>0.01227441703230978</v>
       </c>
       <c r="U17" t="n">
-        <v>0.009576780155115152</v>
+        <v>0.007736076548526278</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0139251251309685</v>
+        <v>0.01365508400205086</v>
       </c>
       <c r="W17" t="n">
-        <v>0.01019580817500492</v>
+        <v>0.009265959544246286</v>
       </c>
       <c r="X17" t="n">
-        <v>0.02079067519451092</v>
+        <v>0.02019431468527703</v>
       </c>
     </row>
     <row r="18">
@@ -1853,61 +1853,61 @@
         <v>31.46666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4515185462382498</v>
+        <v>0.451518546451847</v>
       </c>
       <c r="G18" t="n">
         <v>0.1008878127522195</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2508910324934933</v>
+        <v>0.2508910318037907</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1666097192940944</v>
+        <v>0.1666097196951048</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03009288922194302</v>
+        <v>0.03009288929703804</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2418615173003435</v>
+        <v>0.1810731846415948</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2681515006642515</v>
+        <v>0.2181092683628255</v>
       </c>
       <c r="M18" t="n">
-        <v>4.288454172770764</v>
+        <v>4.276187403986832</v>
       </c>
       <c r="N18" t="n">
-        <v>4.303917415553972</v>
+        <v>4.291835403197044</v>
       </c>
       <c r="O18" t="n">
-        <v>0.006354930986453526</v>
+        <v>0.006119988688782077</v>
       </c>
       <c r="P18" t="n">
-        <v>0.003316946237538857</v>
+        <v>0.002702866377362795</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.00617889385079171</v>
+        <v>0.005999154585284629</v>
       </c>
       <c r="R18" t="n">
-        <v>0.008460450925388378</v>
+        <v>0.007473200511921923</v>
       </c>
       <c r="S18" t="n">
-        <v>0.008839901297548964</v>
+        <v>0.008090665312753785</v>
       </c>
       <c r="T18" t="n">
-        <v>0.01222665699264168</v>
+        <v>0.0119448121924151</v>
       </c>
       <c r="U18" t="n">
-        <v>0.007879625900262787</v>
+        <v>0.007412375456742773</v>
       </c>
       <c r="V18" t="n">
-        <v>0.01296826132184478</v>
+        <v>0.01265969514333957</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0145969988759406</v>
+        <v>0.01366251991852288</v>
       </c>
       <c r="X18" t="n">
-        <v>0.01528863024555051</v>
+        <v>0.01448441209002495</v>
       </c>
     </row>
     <row r="19">
@@ -1933,61 +1933,61 @@
         <v>77.71428571428571</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2928786705374068</v>
+        <v>0.2928786705098768</v>
       </c>
       <c r="G19" t="n">
         <v>0.04084967320261438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2980196009674419</v>
+        <v>0.2980196010147655</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3557027147401188</v>
+        <v>0.3557027147337084</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01254934055241822</v>
+        <v>0.01254934053903507</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1612348717429317</v>
+        <v>0.1079340709237017</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2284373787715951</v>
+        <v>0.1727510320306107</v>
       </c>
       <c r="M19" t="n">
-        <v>3.995533644292064</v>
+        <v>4.005920821418274</v>
       </c>
       <c r="N19" t="n">
-        <v>4.385763809875796</v>
+        <v>4.379023530119922</v>
       </c>
       <c r="O19" t="n">
-        <v>0.00194459338997969</v>
+        <v>0.001814940835121918</v>
       </c>
       <c r="P19" t="n">
-        <v>0.003959370231902597</v>
+        <v>0.003190989711038909</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.003597070675520183</v>
+        <v>0.003556595312604569</v>
       </c>
       <c r="R19" t="n">
-        <v>0.001510380119632769</v>
+        <v>0.001349804416226465</v>
       </c>
       <c r="S19" t="n">
-        <v>0.03201946511225367</v>
+        <v>0.02896522921583519</v>
       </c>
       <c r="T19" t="n">
-        <v>0.007007661678757926</v>
+        <v>0.006829559742851742</v>
       </c>
       <c r="U19" t="n">
-        <v>0.01015180550138561</v>
+        <v>0.009022359902684067</v>
       </c>
       <c r="V19" t="n">
-        <v>0.009274064412685577</v>
+        <v>0.009171924749399691</v>
       </c>
       <c r="W19" t="n">
-        <v>0.006864381470667107</v>
+        <v>0.006570345463227629</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1629009453554489</v>
+        <v>0.1366204167017181</v>
       </c>
     </row>
     <row r="20">
@@ -2013,61 +2013,61 @@
         <v>55.77777777777778</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3719943274037391</v>
+        <v>0.3719943273800574</v>
       </c>
       <c r="G20" t="n">
         <v>0.05691519635742743</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2459185029100323</v>
+        <v>0.2459185030013721</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3196907365948976</v>
+        <v>0.3196907365258876</v>
       </c>
       <c r="J20" t="n">
-        <v>0.005481236733903614</v>
+        <v>0.005481236735255395</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2693988039088081</v>
+        <v>0.2045934972566862</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2994937298866724</v>
+        <v>0.2445265251248257</v>
       </c>
       <c r="M20" t="n">
-        <v>4.607232881973829</v>
+        <v>4.607241387038218</v>
       </c>
       <c r="N20" t="n">
-        <v>4.593855003128358</v>
+        <v>4.59879498485235</v>
       </c>
       <c r="O20" t="n">
-        <v>0.004119698273969235</v>
+        <v>0.003919247495021191</v>
       </c>
       <c r="P20" t="n">
-        <v>0.0004660370212787745</v>
+        <v>1.000000000000011e-05</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.004591309189927666</v>
+        <v>0.004578083742521547</v>
       </c>
       <c r="R20" t="n">
-        <v>0.005455640808046824</v>
+        <v>0.005038553389808509</v>
       </c>
       <c r="S20" t="n">
-        <v>0.01534886885829504</v>
+        <v>0.01269100395002215</v>
       </c>
       <c r="T20" t="n">
-        <v>0.009213643772673278</v>
+        <v>0.008971002112388922</v>
       </c>
       <c r="U20" t="n">
-        <v>0.00821668555849343</v>
+        <v>0.007935543414147619</v>
       </c>
       <c r="V20" t="n">
-        <v>0.01045735940839868</v>
+        <v>0.01039915313514054</v>
       </c>
       <c r="W20" t="n">
-        <v>0.01137763685064642</v>
+        <v>0.01086195564525674</v>
       </c>
       <c r="X20" t="n">
-        <v>0.02904363820603907</v>
+        <v>0.02581650345265067</v>
       </c>
     </row>
     <row r="21">
@@ -2093,61 +2093,61 @@
         <v>17.60714285714286</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3926349948370401</v>
+        <v>0.3926349942752794</v>
       </c>
       <c r="G21" t="n">
         <v>0.1803020058598151</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3377870452012128</v>
+        <v>0.3377870456849771</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08927595410193191</v>
+        <v>0.08927595417992841</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.04831636563563e-18</v>
       </c>
       <c r="K21" t="n">
-        <v>0.120044065289244</v>
+        <v>0.07219559147808233</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1352945028194716</v>
+        <v>0.1375807674251951</v>
       </c>
       <c r="M21" t="n">
-        <v>4.099687029519429</v>
+        <v>4.140908318302595</v>
       </c>
       <c r="N21" t="n">
-        <v>4.1248923715668</v>
+        <v>4.145910995847281</v>
       </c>
       <c r="O21" t="n">
-        <v>0.00407662249469456</v>
+        <v>0.003769891924708079</v>
       </c>
       <c r="P21" t="n">
-        <v>0.01295613900107324</v>
+        <v>0.0124024005593451</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.004952782037304549</v>
+        <v>0.007379913157689356</v>
       </c>
       <c r="R21" t="n">
-        <v>1.000000000027827e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>1.000000000000022e-05</v>
+        <v>1.000000000000014e-05</v>
       </c>
       <c r="T21" t="n">
-        <v>0.009137433873018961</v>
+        <v>0.008852571195289385</v>
       </c>
       <c r="U21" t="n">
-        <v>0.02788412243765577</v>
+        <v>0.0265382321631869</v>
       </c>
       <c r="V21" t="n">
-        <v>0.01435673770158626</v>
+        <v>0.02434217064629895</v>
       </c>
       <c r="W21" t="n">
-        <v>0.01092755132246841</v>
+        <v>0.01269297330453158</v>
       </c>
       <c r="X21" t="n">
-        <v>0.03374527209909096</v>
+        <v>0.05693601364072064</v>
       </c>
     </row>
     <row r="22">
@@ -2173,61 +2173,61 @@
         <v>29.3125</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4135808655857899</v>
+        <v>0.4135808655594087</v>
       </c>
       <c r="G22" t="n">
         <v>0.1083020272785731</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2033297621759581</v>
+        <v>0.203329762176548</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2477420255951969</v>
+        <v>0.247742025507402</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02704531936448205</v>
+        <v>0.02704531947806826</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3065307574048866</v>
+        <v>0.2535001507163447</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3246030519199837</v>
+        <v>0.2746468174846994</v>
       </c>
       <c r="M22" t="n">
-        <v>4.136068433537979</v>
+        <v>4.128946614370499</v>
       </c>
       <c r="N22" t="n">
-        <v>4.310604621520125</v>
+        <v>4.298116970700001</v>
       </c>
       <c r="O22" t="n">
-        <v>0.003445213971254486</v>
+        <v>0.003361516846492695</v>
       </c>
       <c r="P22" t="n">
-        <v>2.268788174050764e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.002660102435005185</v>
+        <v>0.002651885585703412</v>
       </c>
       <c r="R22" t="n">
-        <v>0.003430698613136088</v>
+        <v>0.003186148105360714</v>
       </c>
       <c r="S22" t="n">
-        <v>0.01264827538924559</v>
+        <v>0.01200381895283259</v>
       </c>
       <c r="T22" t="n">
-        <v>0.008861023287704342</v>
+        <v>0.008602907932364045</v>
       </c>
       <c r="U22" t="n">
-        <v>0.008005881075779176</v>
+        <v>0.006614021433434959</v>
       </c>
       <c r="V22" t="n">
-        <v>0.008404846553037061</v>
+        <v>0.008396758203211089</v>
       </c>
       <c r="W22" t="n">
-        <v>0.009121036059921052</v>
+        <v>0.008701089856572706</v>
       </c>
       <c r="X22" t="n">
-        <v>0.02727149539361038</v>
+        <v>0.0260338333428642</v>
       </c>
     </row>
     <row r="23">
@@ -2253,61 +2253,61 @@
         <v>39.58333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6238519511711706</v>
+        <v>0.6238519513177977</v>
       </c>
       <c r="G23" t="n">
         <v>0.08020050125313281</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2028318968739128</v>
+        <v>0.2028318965921395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06932561212208042</v>
+        <v>0.06932561224073039</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0237900385797033</v>
+        <v>0.02379003859619956</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2857665383815918</v>
+        <v>0.2363279958027894</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2907799159926283</v>
+        <v>0.2443814749247547</v>
       </c>
       <c r="M23" t="n">
-        <v>3.864130679318011</v>
+        <v>3.854181525385404</v>
       </c>
       <c r="N23" t="n">
-        <v>4.120494282934716</v>
+        <v>4.093846965401461</v>
       </c>
       <c r="O23" t="n">
-        <v>0.005961437331312818</v>
+        <v>0.005827509522832903</v>
       </c>
       <c r="P23" t="n">
-        <v>0.002420490650410769</v>
+        <v>0.001930602209691899</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.004130001104924606</v>
+        <v>0.003964893243777579</v>
       </c>
       <c r="R23" t="n">
-        <v>0.006793846685857355</v>
+        <v>0.005411720615359649</v>
       </c>
       <c r="S23" t="n">
-        <v>0.02516776405391456</v>
+        <v>0.02323513753987031</v>
       </c>
       <c r="T23" t="n">
-        <v>0.01205297556170596</v>
+        <v>0.01183658616521419</v>
       </c>
       <c r="U23" t="n">
-        <v>0.01094235512893682</v>
+        <v>0.009441826929042395</v>
       </c>
       <c r="V23" t="n">
-        <v>0.009780277397977715</v>
+        <v>0.00958451861337703</v>
       </c>
       <c r="W23" t="n">
-        <v>0.01209869553876791</v>
+        <v>0.01126802690438721</v>
       </c>
       <c r="X23" t="n">
-        <v>0.07851594863145968</v>
+        <v>0.07051814717827196</v>
       </c>
     </row>
     <row r="24">
@@ -2333,61 +2333,61 @@
         <v>18.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5366376492551596</v>
+        <v>0.5366376495537714</v>
       </c>
       <c r="G24" t="n">
         <v>0.1688618709895305</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1622397270835717</v>
+        <v>0.1622397269217724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1157024432834648</v>
+        <v>0.1157024431484001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01655830938827357</v>
+        <v>0.01655830938652574</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3822690760043342</v>
+        <v>0.3277679418815057</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4470791483950528</v>
+        <v>0.4277291089190278</v>
       </c>
       <c r="M24" t="n">
-        <v>4.250849247723202</v>
+        <v>4.117347210101763</v>
       </c>
       <c r="N24" t="n">
-        <v>4.315631253518427</v>
+        <v>4.262493017713639</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01081685253349735</v>
+        <v>0.01068398898360446</v>
       </c>
       <c r="P24" t="n">
-        <v>0.007703572560213488</v>
+        <v>0.007388141622463791</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.0130255083043113</v>
+        <v>0.01275328886727705</v>
       </c>
       <c r="R24" t="n">
-        <v>0.01294350498449111</v>
+        <v>0.01219095645453148</v>
       </c>
       <c r="S24" t="n">
-        <v>0.00512140937954691</v>
+        <v>0.03086638826663004</v>
       </c>
       <c r="T24" t="n">
-        <v>0.02313969012479855</v>
+        <v>0.034668415230471</v>
       </c>
       <c r="U24" t="n">
-        <v>0.01877459816268068</v>
+        <v>0.04316947575877116</v>
       </c>
       <c r="V24" t="n">
-        <v>0.03249401946134126</v>
+        <v>0.04811117458730145</v>
       </c>
       <c r="W24" t="n">
-        <v>0.04108209593454463</v>
+        <v>0.1148754219931374</v>
       </c>
       <c r="X24" t="n">
-        <v>5.667988297074819</v>
+        <v>140.2728113701399</v>
       </c>
     </row>
     <row r="25">
@@ -2413,61 +2413,61 @@
         <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3559522748638808</v>
+        <v>0.3559522750970078</v>
       </c>
       <c r="G25" t="n">
         <v>0.04668534080298786</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2688668009066632</v>
+        <v>0.2688668010518658</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2729559277122325</v>
+        <v>0.2729559273787527</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05553965571423582</v>
+        <v>0.05553965566938588</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2154668003430986</v>
+        <v>0.1551151330948538</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2293733885558452</v>
+        <v>0.1744404709257418</v>
       </c>
       <c r="M25" t="n">
-        <v>4.303014593509248</v>
+        <v>4.304155391582155</v>
       </c>
       <c r="N25" t="n">
-        <v>4.342454821898649</v>
+        <v>4.342588445229381</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0009243203275295116</v>
+        <v>0.000914277827500179</v>
       </c>
       <c r="P25" t="n">
         <v>1e-05</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0005530269389838073</v>
+        <v>0.0006132294782528755</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0003331330087139958</v>
+        <v>0.0003116606984446847</v>
       </c>
       <c r="S25" t="n">
-        <v>9.783676293404874e-05</v>
+        <v>6.970117959606651e-05</v>
       </c>
       <c r="T25" t="n">
-        <v>0.001858507017031442</v>
+        <v>0.001842887793927331</v>
       </c>
       <c r="U25" t="n">
-        <v>0.00119593230768774</v>
+        <v>0.001176768147386531</v>
       </c>
       <c r="V25" t="n">
-        <v>0.001547969601215409</v>
+        <v>0.001615804060575276</v>
       </c>
       <c r="W25" t="n">
-        <v>0.001346818174773276</v>
+        <v>0.001307842896869543</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001313410323274615</v>
+        <v>0.001296395903823144</v>
       </c>
     </row>
     <row r="26">
@@ -2493,61 +2493,61 @@
         <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4002539035826087</v>
+        <v>0.4002539033355717</v>
       </c>
       <c r="G26" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1994618786146296</v>
+        <v>0.199461878586617</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2900964126834302</v>
+        <v>0.2900964128573777</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05246774739927379</v>
+        <v>0.0524677475003759</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3206536186429215</v>
+        <v>0.2666797233848718</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3143408561555466</v>
+        <v>0.2627751303327483</v>
       </c>
       <c r="M26" t="n">
-        <v>4.234787854458681</v>
+        <v>4.221753200887219</v>
       </c>
       <c r="N26" t="n">
-        <v>4.297161793057659</v>
+        <v>4.284272935395412</v>
       </c>
       <c r="O26" t="n">
-        <v>0.001613431803254446</v>
+        <v>0.00158210519702784</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0008943014091062341</v>
+        <v>0.0007094678685056231</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.0007081676253361222</v>
+        <v>0.0006754236345093261</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0005575397425509987</v>
+        <v>0.0004847356892278518</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0003246583029629219</v>
+        <v>0.0002734652633379807</v>
       </c>
       <c r="T26" t="n">
-        <v>0.002680469741764062</v>
+        <v>0.002653873419817038</v>
       </c>
       <c r="U26" t="n">
-        <v>0.001464910474576186</v>
+        <v>0.001333102519337465</v>
       </c>
       <c r="V26" t="n">
-        <v>0.001763129529915675</v>
+        <v>0.00172737067153049</v>
       </c>
       <c r="W26" t="n">
-        <v>0.001519796793220804</v>
+        <v>0.001450409909589445</v>
       </c>
       <c r="X26" t="n">
-        <v>0.001261535720323833</v>
+        <v>0.001235845370002145</v>
       </c>
     </row>
     <row r="27">
@@ -2573,61 +2573,61 @@
         <v>67</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4605706049045288</v>
+        <v>0.4605706047574397</v>
       </c>
       <c r="G27" t="n">
         <v>0.04738213693437573</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2439684145997375</v>
+        <v>0.2439684149537734</v>
       </c>
       <c r="I27" t="n">
-        <v>0.174859558721163</v>
+        <v>0.1748595584867289</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07321928484019485</v>
+        <v>0.07321928486768225</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2430405588533768</v>
+        <v>0.1844609830677478</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3052212311756684</v>
+        <v>0.2508495573201208</v>
       </c>
       <c r="M27" t="n">
-        <v>4.135167174011909</v>
+        <v>4.115975320209331</v>
       </c>
       <c r="N27" t="n">
-        <v>4.152361558197282</v>
+        <v>4.127756835856357</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0008362570910478658</v>
+        <v>0.0008067437199978897</v>
       </c>
       <c r="P27" t="n">
-        <v>0.00032418005317086</v>
+        <v>0.0001434081635684251</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.001195827500999862</v>
+        <v>0.001173212466148055</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0006320535875846396</v>
+        <v>0.0005171130362826565</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0007174695644330698</v>
+        <v>0.0006761806354228812</v>
       </c>
       <c r="T27" t="n">
-        <v>0.001678440569950307</v>
+        <v>0.001637482319988059</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0014695133274421</v>
+        <v>0.001319547563701633</v>
       </c>
       <c r="V27" t="n">
-        <v>0.002443476010021269</v>
+        <v>0.002410411293333479</v>
       </c>
       <c r="W27" t="n">
-        <v>0.001683589948405361</v>
+        <v>0.001574598892946563</v>
       </c>
       <c r="X27" t="n">
-        <v>0.001788220108048311</v>
+        <v>0.001760089473779786</v>
       </c>
     </row>
     <row r="28">
@@ -2653,61 +2653,61 @@
         <v>274.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7158795401171276</v>
+        <v>0.7158795401305122</v>
       </c>
       <c r="G28" t="n">
         <v>0.01156082729280107</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1423140067580003</v>
+        <v>0.1423140067686963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1093709740016232</v>
+        <v>0.1093709739889803</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02087465183044777</v>
+        <v>0.02087465181901007</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3989681985116824</v>
+        <v>0.3641270794280803</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4092626367260103</v>
+        <v>0.3958023988846474</v>
       </c>
       <c r="M28" t="n">
-        <v>4.115059124726736</v>
+        <v>4.118046810694976</v>
       </c>
       <c r="N28" t="n">
-        <v>4.293078289207163</v>
+        <v>4.287790438924369</v>
       </c>
       <c r="O28" t="n">
-        <v>0.001534028668122948</v>
+        <v>0.001538328552308571</v>
       </c>
       <c r="P28" t="n">
-        <v>1e-05</v>
+        <v>1.000000000000005e-05</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.001498306256381639</v>
+        <v>0.001522220425387428</v>
       </c>
       <c r="R28" t="n">
-        <v>0.005015470550394816</v>
+        <v>0.004951719940422409</v>
       </c>
       <c r="S28" t="n">
-        <v>0.01036713362114443</v>
+        <v>0.01013505209317964</v>
       </c>
       <c r="T28" t="n">
-        <v>0.003159243866151763</v>
+        <v>0.003181840887632795</v>
       </c>
       <c r="U28" t="n">
-        <v>0.008255852804250261</v>
+        <v>0.009205415485596535</v>
       </c>
       <c r="V28" t="n">
-        <v>0.003291352599460808</v>
+        <v>0.003393791946027839</v>
       </c>
       <c r="W28" t="n">
-        <v>0.009613434188971235</v>
+        <v>0.01025756547567659</v>
       </c>
       <c r="X28" t="n">
-        <v>0.02351808680518782</v>
+        <v>0.02317866495455673</v>
       </c>
     </row>
     <row r="29">
@@ -2733,61 +2733,61 @@
         <v>15.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5922072970736373</v>
+        <v>0.5922072966992186</v>
       </c>
       <c r="G29" t="n">
         <v>0.2102386208346473</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01553978349820245</v>
+        <v>0.01553978410683548</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1433667741521803</v>
+        <v>0.1433667739479109</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03864752444133265</v>
+        <v>0.03864752441138786</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5374259014890495</v>
+        <v>0.5420877920164093</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3604601450582132</v>
+        <v>0.522889305453539</v>
       </c>
       <c r="M29" t="n">
-        <v>4.282902876970244</v>
+        <v>4.322202820865563</v>
       </c>
       <c r="N29" t="n">
-        <v>4.20670847511995</v>
+        <v>4.268109440207473</v>
       </c>
       <c r="O29" t="n">
-        <v>0.003373715698412262</v>
+        <v>0.003878766615762633</v>
       </c>
       <c r="P29" t="n">
-        <v>0.01785487757802002</v>
+        <v>0.01888218552677088</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0002407743994858941</v>
+        <v>0.0008627578622603392</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01724638504779197</v>
+        <v>0.02115239374430709</v>
       </c>
       <c r="S29" t="n">
-        <v>0.009325626751094608</v>
+        <v>0.01036194886198784</v>
       </c>
       <c r="T29" t="n">
-        <v>0.005132768649515351</v>
+        <v>0.006267378196754303</v>
       </c>
       <c r="U29" t="n">
-        <v>0.07060036645165979</v>
+        <v>0.07505802953975263</v>
       </c>
       <c r="V29" t="n">
-        <v>0.003207955663695086</v>
+        <v>0.003560736423595471</v>
       </c>
       <c r="W29" t="n">
-        <v>0.03459126219839078</v>
+        <v>0.04824849425643082</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01594575176843815</v>
+        <v>0.01785782803572563</v>
       </c>
     </row>
     <row r="30">
@@ -2813,61 +2813,61 @@
         <v>45.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6915723419858851</v>
+        <v>0.6915723419696138</v>
       </c>
       <c r="G30" t="n">
         <v>0.06992518005733864</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07335276932576335</v>
+        <v>0.07335276911610503</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1459822594046087</v>
+        <v>0.1459822596625786</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0191674492264043</v>
+        <v>0.01916744919436398</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5395854534282665</v>
+        <v>0.5263699752913374</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4064083083468841</v>
+        <v>0.4504027580945141</v>
       </c>
       <c r="M30" t="n">
-        <v>4.572095310020834</v>
+        <v>4.570742595230626</v>
       </c>
       <c r="N30" t="n">
-        <v>4.309233995967086</v>
+        <v>4.317443697018121</v>
       </c>
       <c r="O30" t="n">
-        <v>0.001974519084271798</v>
+        <v>0.002067387902453597</v>
       </c>
       <c r="P30" t="n">
-        <v>0.00390890685602701</v>
+        <v>0.004223668512174508</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0002397164832904759</v>
+        <v>0.0003169382615374674</v>
       </c>
       <c r="R30" t="n">
-        <v>0.009421758159677473</v>
+        <v>0.009938290943063406</v>
       </c>
       <c r="S30" t="n">
-        <v>0.004179007006160515</v>
+        <v>0.0044865942196676</v>
       </c>
       <c r="T30" t="n">
-        <v>0.003400984404660079</v>
+        <v>0.003621280925258424</v>
       </c>
       <c r="U30" t="n">
-        <v>0.007040312805388546</v>
+        <v>0.007635707588426299</v>
       </c>
       <c r="V30" t="n">
-        <v>0.003092136185444864</v>
+        <v>0.003244128382149677</v>
       </c>
       <c r="W30" t="n">
-        <v>0.0163811158801954</v>
+        <v>0.01812369430066589</v>
       </c>
       <c r="X30" t="n">
-        <v>0.005717630277732708</v>
+        <v>0.006237162548852759</v>
       </c>
     </row>
     <row r="31">
@@ -2893,61 +2893,61 @@
         <v>26.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5100618132893889</v>
+        <v>0.510061813306836</v>
       </c>
       <c r="G31" t="n">
         <v>0.1207073450419458</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08244690044211486</v>
+        <v>0.08244690045861332</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2664816652636977</v>
+        <v>0.2664816652601923</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02030227596285282</v>
+        <v>0.02030227593241257</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4939662194456111</v>
+        <v>0.4787482540209079</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4304051842043197</v>
+        <v>0.4351165754737921</v>
       </c>
       <c r="M31" t="n">
-        <v>4.280086717342922</v>
+        <v>4.278628979684508</v>
       </c>
       <c r="N31" t="n">
-        <v>4.392091923124475</v>
+        <v>4.390877193702263</v>
       </c>
       <c r="O31" t="n">
-        <v>0.002212569642459092</v>
+        <v>0.002201474452063921</v>
       </c>
       <c r="P31" t="n">
-        <v>0.005756204075930939</v>
+        <v>0.005753689933667507</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0002681450838371158</v>
+        <v>0.0002574077180274379</v>
       </c>
       <c r="R31" t="n">
-        <v>0.001796872263137101</v>
+        <v>0.001778407350455104</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0005729792831041041</v>
+        <v>0.00055974572474833</v>
       </c>
       <c r="T31" t="n">
-        <v>0.003720448129265789</v>
+        <v>0.003740356175967931</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01265458249049705</v>
+        <v>0.01302328158800875</v>
       </c>
       <c r="V31" t="n">
-        <v>0.002572472276813907</v>
+        <v>0.002621383751430529</v>
       </c>
       <c r="W31" t="n">
-        <v>0.003043422605614916</v>
+        <v>0.003153010239280609</v>
       </c>
       <c r="X31" t="n">
-        <v>0.002831167689119767</v>
+        <v>0.002893850745856871</v>
       </c>
     </row>
     <row r="32">
@@ -2973,61 +2973,61 @@
         <v>32.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6207177798737793</v>
+        <v>0.6207177798836309</v>
       </c>
       <c r="G32" t="n">
         <v>0.09738046547862497</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1026556514757471</v>
+        <v>0.102655651448909</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1515085776379964</v>
+        <v>0.1515085776593587</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02773752553385222</v>
+        <v>0.0277375255294765</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5041910255103661</v>
+        <v>0.4809602673783849</v>
       </c>
       <c r="L32" t="n">
-        <v>0.427252988656721</v>
+        <v>0.4335280661008496</v>
       </c>
       <c r="M32" t="n">
-        <v>4.563241224115946</v>
+        <v>4.566585713233426</v>
       </c>
       <c r="N32" t="n">
-        <v>4.417612467237852</v>
+        <v>4.415995232459434</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0006691893135036334</v>
+        <v>0.0006847788751482901</v>
       </c>
       <c r="P32" t="n">
-        <v>0.00405671385392055</v>
+        <v>0.004157373419996939</v>
       </c>
       <c r="Q32" t="n">
         <v>1e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>0.004431448153823202</v>
+        <v>0.004560549769790144</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001410318523168742</v>
+        <v>0.001422755174828777</v>
       </c>
       <c r="T32" t="n">
-        <v>0.002112257329904021</v>
+        <v>0.002137869252250389</v>
       </c>
       <c r="U32" t="n">
-        <v>0.008645398930070245</v>
+        <v>0.00906382775149874</v>
       </c>
       <c r="V32" t="n">
-        <v>0.00260731026014895</v>
+        <v>0.002630002707977629</v>
       </c>
       <c r="W32" t="n">
-        <v>0.00813856008353521</v>
+        <v>0.008753552894219764</v>
       </c>
       <c r="X32" t="n">
-        <v>0.003607290030651333</v>
+        <v>0.003659202178161485</v>
       </c>
     </row>
     <row r="33">
@@ -3051,61 +3051,61 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.6421516036650835</v>
+        <v>0.642151603719554</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002523163010079717</v>
+        <v>0.002523163255140709</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2245698007084695</v>
+        <v>0.2245698005775707</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1058026140953321</v>
+        <v>0.1058026139657058</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02495281852103528</v>
+        <v>0.0249528184820288</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2828125477845588</v>
+        <v>0.2241840487608926</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2943164256458368</v>
+        <v>0.2571359088954341</v>
       </c>
       <c r="M33" t="n">
-        <v>4.275571175206728</v>
+        <v>4.264159583875831</v>
       </c>
       <c r="N33" t="n">
-        <v>4.266011128939271</v>
+        <v>4.255131042121516</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003721062055523678</v>
+        <v>0.003568178526699263</v>
       </c>
       <c r="P33" t="n">
-        <v>0.002004240594218346</v>
+        <v>0.001369238678037555</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003536156447389961</v>
+        <v>0.003487948926234275</v>
       </c>
       <c r="R33" t="n">
-        <v>0.007089830074720422</v>
+        <v>0.006267396568362716</v>
       </c>
       <c r="S33" t="n">
-        <v>0.003920018428343979</v>
+        <v>0.003504997178617085</v>
       </c>
       <c r="T33" t="n">
-        <v>0.00707167874812322</v>
+        <v>0.006824545208163823</v>
       </c>
       <c r="U33" t="n">
-        <v>0.01473158019449354</v>
+        <v>0.01694966701772099</v>
       </c>
       <c r="V33" t="n">
-        <v>0.007670801010774816</v>
+        <v>0.007667227435563432</v>
       </c>
       <c r="W33" t="n">
-        <v>0.01264043800390412</v>
+        <v>0.01247886591581</v>
       </c>
       <c r="X33" t="n">
-        <v>0.007300489826997365</v>
+        <v>0.00700996516223948</v>
       </c>
     </row>
     <row r="34">
@@ -3131,61 +3131,61 @@
         <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7519633395058384</v>
+        <v>0.7519633396250179</v>
       </c>
       <c r="G34" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01478397129559729</v>
+        <v>0.0147839710365304</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1023682012617217</v>
+        <v>0.1023682013871307</v>
       </c>
       <c r="J34" t="n">
-        <v>0.008784365836720525</v>
+        <v>0.008784365851198749</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5387040856238987</v>
+        <v>0.5349473716287773</v>
       </c>
       <c r="L34" t="n">
-        <v>0.450881926604315</v>
+        <v>0.5382437891085146</v>
       </c>
       <c r="M34" t="n">
-        <v>4.291280449636701</v>
+        <v>4.267183287460422</v>
       </c>
       <c r="N34" t="n">
-        <v>4.281735804523738</v>
+        <v>4.312129425377156</v>
       </c>
       <c r="O34" t="n">
-        <v>0.004690073035452948</v>
+        <v>0.006214857362383317</v>
       </c>
       <c r="P34" t="n">
-        <v>0.01275303187543643</v>
+        <v>0.01699926117595317</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.003072390407171038</v>
+        <v>0.003612240519342102</v>
       </c>
       <c r="R34" t="n">
-        <v>0.01470118427902963</v>
+        <v>0.01759639272267261</v>
       </c>
       <c r="S34" t="n">
-        <v>0.008497861375679708</v>
+        <v>0.01047895134576164</v>
       </c>
       <c r="T34" t="n">
-        <v>0.006428896915307041</v>
+        <v>0.009742875937494545</v>
       </c>
       <c r="U34" t="n">
-        <v>0.0470266747129684</v>
+        <v>0.08251836770906038</v>
       </c>
       <c r="V34" t="n">
-        <v>0.005846986622031445</v>
+        <v>0.005137753961292672</v>
       </c>
       <c r="W34" t="n">
-        <v>0.01879655583935826</v>
+        <v>0.02269479885129614</v>
       </c>
       <c r="X34" t="n">
-        <v>0.007457564664721176</v>
+        <v>0.00896963025683536</v>
       </c>
     </row>
     <row r="35">
@@ -3211,61 +3211,61 @@
         <v>74.09999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.687523750659823</v>
+        <v>0.6875237506860816</v>
       </c>
       <c r="G35" t="n">
         <v>0.042842148105306</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2018749037744333</v>
+        <v>0.201874903841659</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03464191229956181</v>
+        <v>0.03464191218332047</v>
       </c>
       <c r="J35" t="n">
-        <v>0.033117285160876</v>
+        <v>0.03311728518363292</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3025718444011018</v>
+        <v>0.2459581993328201</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2499236069255949</v>
+        <v>0.2359432290159188</v>
       </c>
       <c r="M35" t="n">
-        <v>4.05737490915139</v>
+        <v>3.975752990096821</v>
       </c>
       <c r="N35" t="n">
-        <v>4.15193336697933</v>
+        <v>4.147857086953065</v>
       </c>
       <c r="O35" t="n">
-        <v>0.001235491514101082</v>
+        <v>0.001238793578734914</v>
       </c>
       <c r="P35" t="n">
-        <v>0.03357969006695641</v>
+        <v>0.499999999994706</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.000607835107932592</v>
+        <v>0.0005745121579241243</v>
       </c>
       <c r="R35" t="n">
-        <v>0.004849918034519818</v>
+        <v>0.004464426784697684</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0009582475394005796</v>
+        <v>0.0009130636002167316</v>
       </c>
       <c r="T35" t="n">
-        <v>0.002458002565470871</v>
+        <v>0.00249638531683662</v>
       </c>
       <c r="U35" t="n">
-        <v>12.26788287907425</v>
+        <v>6468.60806307083</v>
       </c>
       <c r="V35" t="n">
-        <v>0.002253364702528688</v>
+        <v>0.002162074040936976</v>
       </c>
       <c r="W35" t="n">
-        <v>0.02096471033507092</v>
+        <v>0.0264080285028549</v>
       </c>
       <c r="X35" t="n">
-        <v>0.00267476923513267</v>
+        <v>0.002533509250058015</v>
       </c>
     </row>
     <row r="36">
@@ -3291,61 +3291,61 @@
         <v>46.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6184344404805445</v>
+        <v>0.6184344404849657</v>
       </c>
       <c r="G36" t="n">
         <v>0.06871435442864013</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1345326977341799</v>
+        <v>0.1345326978111002</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1554100927459354</v>
+        <v>0.1554100926475006</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02290841461070009</v>
+        <v>0.0229084146277933</v>
       </c>
       <c r="K36" t="n">
-        <v>0.432114221689511</v>
+        <v>0.3970681303962988</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3934889538239607</v>
+        <v>0.3691396770741446</v>
       </c>
       <c r="M36" t="n">
-        <v>4.321952334671811</v>
+        <v>4.31291763426113</v>
       </c>
       <c r="N36" t="n">
-        <v>4.315700192215298</v>
+        <v>4.307550674780784</v>
       </c>
       <c r="O36" t="n">
-        <v>0.001008408305604739</v>
+        <v>0.0009752856063394406</v>
       </c>
       <c r="P36" t="n">
-        <v>0.002032393319238109</v>
+        <v>0.001885358814981861</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0004101598320585874</v>
+        <v>0.0003696677089741656</v>
       </c>
       <c r="R36" t="n">
-        <v>0.001946913991492018</v>
+        <v>0.001796481143817508</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001319761917042878</v>
+        <v>0.001225826330714774</v>
       </c>
       <c r="T36" t="n">
-        <v>0.002451026684508723</v>
+        <v>0.002408295631550217</v>
       </c>
       <c r="U36" t="n">
-        <v>0.004383101792824889</v>
+        <v>0.004289421944219651</v>
       </c>
       <c r="V36" t="n">
-        <v>0.002570189462926131</v>
+        <v>0.002541248684783677</v>
       </c>
       <c r="W36" t="n">
-        <v>0.003645233782416663</v>
+        <v>0.003540194813886496</v>
       </c>
       <c r="X36" t="n">
-        <v>0.004543354136486776</v>
+        <v>0.00446015982795111</v>
       </c>
     </row>
     <row r="37">
@@ -3371,61 +3371,61 @@
         <v>55</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4310490712245829</v>
+        <v>0.4310490710111513</v>
       </c>
       <c r="G37" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3585099706610048</v>
+        <v>0.3585099709374001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1452580722152676</v>
+        <v>0.1452580721451264</v>
       </c>
       <c r="J37" t="n">
-        <v>0.007462828179086988</v>
+        <v>0.007462828186264588</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1035375728459106</v>
+        <v>0.05755759486930409</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1171591017568475</v>
+        <v>0.07037544686481832</v>
       </c>
       <c r="M37" t="n">
-        <v>4.240813110988225</v>
+        <v>4.231556993851775</v>
       </c>
       <c r="N37" t="n">
-        <v>4.271074928022523</v>
+        <v>4.25944927929172</v>
       </c>
       <c r="O37" t="n">
-        <v>0.001425162358900785</v>
+        <v>0.001411953332965493</v>
       </c>
       <c r="P37" t="n">
-        <v>0.0007042530275524824</v>
+        <v>0.0005308925374675324</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.001266376324922782</v>
+        <v>0.001238268956759675</v>
       </c>
       <c r="R37" t="n">
-        <v>0.0008579992845053234</v>
+        <v>0.0007195752296837749</v>
       </c>
       <c r="S37" t="n">
-        <v>0.002392319415189669</v>
+        <v>0.001941661451422511</v>
       </c>
       <c r="T37" t="n">
-        <v>0.003382033435560812</v>
+        <v>0.003388881794729776</v>
       </c>
       <c r="U37" t="n">
-        <v>0.001953206244000848</v>
+        <v>0.001732636046821254</v>
       </c>
       <c r="V37" t="n">
-        <v>0.003324412793488031</v>
+        <v>0.003259045859891605</v>
       </c>
       <c r="W37" t="n">
-        <v>0.002588786613463288</v>
+        <v>0.002435066960314566</v>
       </c>
       <c r="X37" t="n">
-        <v>0.005950532131247049</v>
+        <v>0.00495462571990293</v>
       </c>
     </row>
     <row r="38">
@@ -3451,61 +3451,61 @@
         <v>23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4115513533477569</v>
+        <v>0.4115513534924096</v>
       </c>
       <c r="G38" t="n">
         <v>0.1380262249827467</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3184506857669814</v>
+        <v>0.318450685478181</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1287866383384099</v>
+        <v>0.1287866384976123</v>
       </c>
       <c r="J38" t="n">
-        <v>0.003185097564105027</v>
+        <v>0.003185097549050355</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1433109613706779</v>
+        <v>0.08996212189252457</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1277231843256094</v>
+        <v>0.07845262483669468</v>
       </c>
       <c r="M38" t="n">
-        <v>4.158873949626578</v>
+        <v>4.142537911135626</v>
       </c>
       <c r="N38" t="n">
-        <v>4.19896969761463</v>
+        <v>4.181514285095943</v>
       </c>
       <c r="O38" t="n">
-        <v>0.001825414876281545</v>
+        <v>0.001821516998801657</v>
       </c>
       <c r="P38" t="n">
-        <v>0.0005234447571410045</v>
+        <v>0.0004545855591582402</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0008139357655750706</v>
+        <v>0.0007913467313133458</v>
       </c>
       <c r="R38" t="n">
-        <v>0.000482220560484867</v>
+        <v>0.0003414255621984318</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0005737900523037063</v>
+        <v>5.769017423952701e-05</v>
       </c>
       <c r="T38" t="n">
-        <v>0.004255555693477111</v>
+        <v>0.004294365474760113</v>
       </c>
       <c r="U38" t="n">
-        <v>0.001644605051547562</v>
+        <v>0.001593772130123952</v>
       </c>
       <c r="V38" t="n">
-        <v>0.002641107026599577</v>
+        <v>0.002594381808410473</v>
       </c>
       <c r="W38" t="n">
-        <v>0.002168068381011788</v>
+        <v>0.002028927905630326</v>
       </c>
       <c r="X38" t="n">
-        <v>0.003515432887186348</v>
+        <v>0.002764382557497266</v>
       </c>
     </row>
     <row r="39">
@@ -3531,61 +3531,61 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>0.464866072408512</v>
+        <v>0.4648660724078407</v>
       </c>
       <c r="G39" t="n">
         <v>0.06613756613756613</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3147165341115007</v>
+        <v>0.3147165341147267</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1215057334841287</v>
+        <v>0.1215057334732506</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03277409385829239</v>
+        <v>0.03277409386661587</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1521632323991432</v>
+        <v>0.09663475671709176</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1365428260454886</v>
+        <v>0.08937829104078603</v>
       </c>
       <c r="M39" t="n">
-        <v>4.276604215929122</v>
+        <v>4.263201611065282</v>
       </c>
       <c r="N39" t="n">
-        <v>4.264390543388925</v>
+        <v>4.252803795564823</v>
       </c>
       <c r="O39" t="n">
-        <v>0.001637116370510771</v>
+        <v>0.001601926198531034</v>
       </c>
       <c r="P39" t="n">
-        <v>0.0005290314786350071</v>
+        <v>0.0003366431932689329</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.001084462504970598</v>
+        <v>0.001056129011225323</v>
       </c>
       <c r="R39" t="n">
-        <v>0.002336353455538666</v>
+        <v>0.002068451229250729</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001427733491618876</v>
+        <v>0.001309882693735642</v>
       </c>
       <c r="T39" t="n">
-        <v>0.003254718186188554</v>
+        <v>0.003227767439206243</v>
       </c>
       <c r="U39" t="n">
-        <v>0.002493280819482371</v>
+        <v>0.002371673099018905</v>
       </c>
       <c r="V39" t="n">
-        <v>0.002868773500442054</v>
+        <v>0.00282758889230128</v>
       </c>
       <c r="W39" t="n">
-        <v>0.004050400060356956</v>
+        <v>0.003832823743408251</v>
       </c>
       <c r="X39" t="n">
-        <v>0.003026371867615176</v>
+        <v>0.002961679939955286</v>
       </c>
     </row>
     <row r="40">
@@ -3611,61 +3611,61 @@
         <v>70.70000000000002</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4301189564620539</v>
+        <v>0.4301189564542686</v>
       </c>
       <c r="G40" t="n">
         <v>0.04490244942861631</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1726240369116226</v>
+        <v>0.1726240368983525</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3491894964880415</v>
+        <v>0.3491894964967999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.003165060709665684</v>
+        <v>0.00316506072196271</v>
       </c>
       <c r="K40" t="n">
-        <v>0.3688466951349098</v>
+        <v>0.3237270084783151</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4215702660386719</v>
+        <v>0.4058096318217366</v>
       </c>
       <c r="M40" t="n">
-        <v>4.285314308507465</v>
+        <v>4.305896102470063</v>
       </c>
       <c r="N40" t="n">
-        <v>4.522372402886067</v>
+        <v>4.52283996631046</v>
       </c>
       <c r="O40" t="n">
-        <v>0.00305572068937045</v>
+        <v>0.002967551034117766</v>
       </c>
       <c r="P40" t="n">
-        <v>0.002057870532167546</v>
+        <v>0.001924048823906845</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.002640266168819202</v>
+        <v>0.002569223876152503</v>
       </c>
       <c r="R40" t="n">
-        <v>0.002586823653348626</v>
+        <v>0.002482338347813527</v>
       </c>
       <c r="S40" t="n">
-        <v>0.06829342157360137</v>
+        <v>0.05958104088100127</v>
       </c>
       <c r="T40" t="n">
-        <v>0.005455935642185071</v>
+        <v>0.005278816435922988</v>
       </c>
       <c r="U40" t="n">
-        <v>0.003779813403649733</v>
+        <v>0.003907267632847188</v>
       </c>
       <c r="V40" t="n">
-        <v>0.005224420103971402</v>
+        <v>0.005201350624590483</v>
       </c>
       <c r="W40" t="n">
-        <v>0.004129327668762856</v>
+        <v>0.004082749806083402</v>
       </c>
       <c r="X40" t="n">
-        <v>0.3191336579248548</v>
+        <v>0.2773871666828474</v>
       </c>
     </row>
     <row r="41">
@@ -3691,61 +3691,61 @@
         <v>84.84</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3369254806988865</v>
+        <v>0.3369254807409055</v>
       </c>
       <c r="G41" t="n">
         <v>0.03741870785718027</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2464337952095151</v>
+        <v>0.2464337951089697</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3649923484168429</v>
+        <v>0.3649923484758453</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01422966781757511</v>
+        <v>0.0142296678170992</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2573692328562169</v>
+        <v>0.195223836174422</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2816505847648225</v>
+        <v>0.2298287918943051</v>
       </c>
       <c r="M41" t="n">
-        <v>4.427001902537881</v>
+        <v>4.426831872784585</v>
       </c>
       <c r="N41" t="n">
-        <v>4.510730467141761</v>
+        <v>4.510924526744252</v>
       </c>
       <c r="O41" t="n">
-        <v>0.0009500418828095761</v>
+        <v>0.0008928117249336103</v>
       </c>
       <c r="P41" t="n">
-        <v>0.001519138908458736</v>
+        <v>0.001200632270871777</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.0009880834625147371</v>
+        <v>0.0009565423617101247</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0009572293940618721</v>
+        <v>0.0008729991275740937</v>
       </c>
       <c r="S41" t="n">
-        <v>0.003909895543498093</v>
+        <v>0.003543875067036561</v>
       </c>
       <c r="T41" t="n">
-        <v>0.002069633002748705</v>
+        <v>0.002011491431704259</v>
       </c>
       <c r="U41" t="n">
-        <v>0.002810303370777496</v>
+        <v>0.002519416462177359</v>
       </c>
       <c r="V41" t="n">
-        <v>0.002236264329211602</v>
+        <v>0.002189925643314253</v>
       </c>
       <c r="W41" t="n">
-        <v>0.002145592130382356</v>
+        <v>0.002051471419447568</v>
       </c>
       <c r="X41" t="n">
-        <v>0.006854095818438511</v>
+        <v>0.006342029050505042</v>
       </c>
     </row>
     <row r="42">
@@ -3771,61 +3771,61 @@
         <v>124.31</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4255446328458828</v>
+        <v>0.4255446328415167</v>
       </c>
       <c r="G42" t="n">
         <v>0.02553779401981477</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2146647956812922</v>
+        <v>0.214664795708344</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3235805049574504</v>
+        <v>0.3235805049438804</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01067227249555984</v>
+        <v>0.01067227248644411</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3161275935169219</v>
+        <v>0.1321655280991434</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4156924764765986</v>
+        <v>0.365697815930521</v>
       </c>
       <c r="M42" t="n">
-        <v>4.505860957774482</v>
+        <v>2.437951428744338</v>
       </c>
       <c r="N42" t="n">
-        <v>4.560556223119185</v>
+        <v>4.467575341091654</v>
       </c>
       <c r="O42" t="n">
-        <v>0.003651458440397529</v>
+        <v>0.003523378395882515</v>
       </c>
       <c r="P42" t="n">
-        <v>0.002769114672656786</v>
+        <v>0.002120567957811756</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.004448160031034519</v>
+        <v>0.004355676941402375</v>
       </c>
       <c r="R42" t="n">
-        <v>0.003022134261803278</v>
+        <v>0.002787711204889287</v>
       </c>
       <c r="S42" t="n">
-        <v>1e-05</v>
+        <v>0.4546754774370763</v>
       </c>
       <c r="T42" t="n">
-        <v>0.01052805584603005</v>
+        <v>0.007819148031134378</v>
       </c>
       <c r="U42" t="n">
-        <v>0.02670503346172724</v>
+        <v>0.009060865342855351</v>
       </c>
       <c r="V42" t="n">
-        <v>0.01321160577444688</v>
+        <v>0.01221703152378325</v>
       </c>
       <c r="W42" t="n">
-        <v>0.01185487467948383</v>
+        <v>0.006591637390929282</v>
       </c>
       <c r="X42" t="n">
-        <v>2.997004699652758</v>
+        <v>22135.30562610104</v>
       </c>
     </row>
     <row r="43">
@@ -3851,61 +3851,61 @@
         <v>40.1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5997176448026437</v>
+        <v>0.5997176446896944</v>
       </c>
       <c r="G43" t="n">
         <v>0.0791671614614258</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2378772798847145</v>
+        <v>0.2378772801295146</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05923193023736853</v>
+        <v>0.05923193014095748</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0240059836138475</v>
+        <v>0.02400598357840774</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2407342940451179</v>
+        <v>0.1864807199699899</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3927190908536731</v>
+        <v>0.3818637018680048</v>
       </c>
       <c r="M43" t="n">
-        <v>3.957365255938519</v>
+        <v>3.965151146825701</v>
       </c>
       <c r="N43" t="n">
-        <v>4.264301149782977</v>
+        <v>4.256611868595258</v>
       </c>
       <c r="O43" t="n">
-        <v>0.01650073159060361</v>
+        <v>0.01741878548928298</v>
       </c>
       <c r="P43" t="n">
-        <v>0.01009373946972511</v>
+        <v>0.00928726170015853</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.02012075479610474</v>
+        <v>0.02093302296108103</v>
       </c>
       <c r="R43" t="n">
-        <v>0.023315156969651</v>
+        <v>0.02089196513303763</v>
       </c>
       <c r="S43" t="n">
-        <v>0.06404396287004575</v>
+        <v>0.06039259869751168</v>
       </c>
       <c r="T43" t="n">
-        <v>0.02696423755600144</v>
+        <v>0.02808654891663384</v>
       </c>
       <c r="U43" t="n">
-        <v>0.01971495154421146</v>
+        <v>0.02040412833310027</v>
       </c>
       <c r="V43" t="n">
-        <v>0.04695142407328909</v>
+        <v>0.04948955257036129</v>
       </c>
       <c r="W43" t="n">
-        <v>0.04504354430141226</v>
+        <v>0.05032619788391101</v>
       </c>
       <c r="X43" t="n">
-        <v>0.1735378555651444</v>
+        <v>0.164557882784434</v>
       </c>
     </row>
     <row r="44">
@@ -3931,61 +3931,61 @@
         <v>25.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3587984910438237</v>
+        <v>0.3587984911488203</v>
       </c>
       <c r="G44" t="n">
         <v>0.1259763164525069</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2964643700107539</v>
+        <v>0.2964643700757857</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1968371786437586</v>
+        <v>0.1968371786061268</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02192364384915694</v>
+        <v>0.02192364371676016</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1729821644702371</v>
+        <v>0.1160040171888872</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3961689454705551</v>
+        <v>0.3741130630197994</v>
       </c>
       <c r="M44" t="n">
-        <v>4.220618689085988</v>
+        <v>4.221992695387505</v>
       </c>
       <c r="N44" t="n">
-        <v>4.393130684049197</v>
+        <v>4.382687577846458</v>
       </c>
       <c r="O44" t="n">
-        <v>0.02583827132454846</v>
+        <v>0.02503885560291694</v>
       </c>
       <c r="P44" t="n">
-        <v>0.01266471581677057</v>
+        <v>0.01145670772608285</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.02392022453591427</v>
+        <v>0.02412383864671729</v>
       </c>
       <c r="R44" t="n">
-        <v>0.01203067736005225</v>
+        <v>0.01083471410970834</v>
       </c>
       <c r="S44" t="n">
-        <v>0.02332355470578531</v>
+        <v>0.02034455942920898</v>
       </c>
       <c r="T44" t="n">
-        <v>0.05348613224703609</v>
+        <v>0.05262933432759823</v>
       </c>
       <c r="U44" t="n">
-        <v>0.02241826353741333</v>
+        <v>0.02129510617980311</v>
       </c>
       <c r="V44" t="n">
-        <v>0.05596917486159735</v>
+        <v>0.05649983870957816</v>
       </c>
       <c r="W44" t="n">
-        <v>0.02292320361049745</v>
+        <v>0.02225560953875284</v>
       </c>
       <c r="X44" t="n">
-        <v>0.04711065153991716</v>
+        <v>0.04259830562584577</v>
       </c>
     </row>
     <row r="45">
@@ -4011,61 +4011,61 @@
         <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4805050132618147</v>
+        <v>0.4805050130472089</v>
       </c>
       <c r="G45" t="n">
         <v>0.1587301587301587</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1510431451475349</v>
+        <v>0.1510431452397918</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1848438942219129</v>
+        <v>0.1848438943574318</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02487778863857871</v>
+        <v>0.02487778862540869</v>
       </c>
       <c r="K45" t="n">
-        <v>0.402064738426252</v>
+        <v>0.3599855396326003</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3475433572858478</v>
+        <v>0.4783661489839898</v>
       </c>
       <c r="M45" t="n">
-        <v>4.273822963139304</v>
+        <v>4.246879291334123</v>
       </c>
       <c r="N45" t="n">
-        <v>4.372632385419013</v>
+        <v>4.418143141072385</v>
       </c>
       <c r="O45" t="n">
-        <v>0.07135366522764755</v>
+        <v>0.07721318724752355</v>
       </c>
       <c r="P45" t="n">
-        <v>0.08746748301265329</v>
+        <v>0.08165383378851238</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.06618598023413179</v>
+        <v>0.05374227184681066</v>
       </c>
       <c r="R45" t="n">
-        <v>0.1047651963502601</v>
+        <v>0.09354469738887861</v>
       </c>
       <c r="S45" t="n">
-        <v>0.1300631539439227</v>
+        <v>0.1170555418879767</v>
       </c>
       <c r="T45" t="n">
-        <v>0.2005940886136379</v>
+        <v>0.2387521997243088</v>
       </c>
       <c r="U45" t="n">
-        <v>0.2430199268960533</v>
+        <v>0.2281067442919686</v>
       </c>
       <c r="V45" t="n">
-        <v>0.2149393707298246</v>
+        <v>0.1575811073357216</v>
       </c>
       <c r="W45" t="n">
-        <v>0.2743122140323959</v>
+        <v>0.2510208253819348</v>
       </c>
       <c r="X45" t="n">
-        <v>0.4947255431501673</v>
+        <v>0.428954894954261</v>
       </c>
     </row>
     <row r="46">
@@ -4091,61 +4091,61 @@
         <v>13.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4123104193140011</v>
+        <v>0.4123104194730447</v>
       </c>
       <c r="G46" t="n">
         <v>0.2300437083045778</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09500900007204896</v>
+        <v>0.09500899989902098</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2190898484594311</v>
+        <v>0.2190898485295714</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04354702384994095</v>
+        <v>0.04354702379378513</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4152342674066459</v>
+        <v>0.4033453330186448</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3811288988599959</v>
+        <v>0.4829174272706265</v>
       </c>
       <c r="M46" t="n">
-        <v>3.736658907187545</v>
+        <v>3.778791310898719</v>
       </c>
       <c r="N46" t="n">
-        <v>4.494678572468655</v>
+        <v>4.476138985560363</v>
       </c>
       <c r="O46" t="n">
-        <v>0.05363566340805416</v>
+        <v>0.05723791518464611</v>
       </c>
       <c r="P46" t="n">
-        <v>0.03396261609905674</v>
+        <v>0.03626836816374761</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.02748023772924122</v>
+        <v>0.0260050953034355</v>
       </c>
       <c r="R46" t="n">
-        <v>0.0353713838733486</v>
+        <v>0.03759145692939202</v>
       </c>
       <c r="S46" t="n">
-        <v>0.1907982781147629</v>
+        <v>0.1835181336955814</v>
       </c>
       <c r="T46" t="n">
-        <v>0.1290100766926578</v>
+        <v>0.1426681598118602</v>
       </c>
       <c r="U46" t="n">
-        <v>0.06374704627368719</v>
+        <v>0.06909445818938392</v>
       </c>
       <c r="V46" t="n">
-        <v>0.05439885402576789</v>
+        <v>0.04936457394642008</v>
       </c>
       <c r="W46" t="n">
-        <v>0.0542414767917497</v>
+        <v>0.05987798004059705</v>
       </c>
       <c r="X46" t="n">
-        <v>2.18989719978157</v>
+        <v>1.947164228176619</v>
       </c>
     </row>
     <row r="47">
@@ -4171,61 +4171,61 @@
         <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4235443992070436</v>
+        <v>0.4235443991299785</v>
       </c>
       <c r="G47" t="n">
         <v>0.1670843776106934</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2433419961172016</v>
+        <v>0.2433419961113411</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1505472905220324</v>
+        <v>0.1505472906218897</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01548193654302897</v>
+        <v>0.01548193652609739</v>
       </c>
       <c r="K47" t="n">
-        <v>0.249759804799666</v>
+        <v>0.1903563654068834</v>
       </c>
       <c r="L47" t="n">
-        <v>0.4066190590329566</v>
+        <v>0.3842019128456324</v>
       </c>
       <c r="M47" t="n">
-        <v>4.226749871470481</v>
+        <v>4.218169191500397</v>
       </c>
       <c r="N47" t="n">
-        <v>4.358112882208157</v>
+        <v>4.348273340283221</v>
       </c>
       <c r="O47" t="n">
-        <v>0.02408535121683737</v>
+        <v>0.02388964727333836</v>
       </c>
       <c r="P47" t="n">
-        <v>0.01273485839807877</v>
+        <v>0.0117109230293584</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.02262674046730047</v>
+        <v>0.0220934122447036</v>
       </c>
       <c r="R47" t="n">
-        <v>0.01773005861029248</v>
+        <v>0.01571826113479599</v>
       </c>
       <c r="S47" t="n">
-        <v>0.02607332262035277</v>
+        <v>0.02286303104447078</v>
       </c>
       <c r="T47" t="n">
-        <v>0.04649709426130562</v>
+        <v>0.04717966769565809</v>
       </c>
       <c r="U47" t="n">
-        <v>0.02148883897366578</v>
+        <v>0.02068033485131231</v>
       </c>
       <c r="V47" t="n">
-        <v>0.05469316239144191</v>
+        <v>0.05314571731651224</v>
       </c>
       <c r="W47" t="n">
-        <v>0.03119668402963288</v>
+        <v>0.03076133595508825</v>
       </c>
       <c r="X47" t="n">
-        <v>0.04818002473516954</v>
+        <v>0.04606634081454698</v>
       </c>
     </row>
     <row r="48">
@@ -4251,61 +4251,61 @@
         <v>26.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4466462867107708</v>
+        <v>0.4466462865765082</v>
       </c>
       <c r="G48" t="n">
         <v>0.1197963462114405</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3318502634836513</v>
+        <v>0.3318502636697235</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06116662707319055</v>
+        <v>0.06116662702741293</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04054047652094685</v>
+        <v>0.04054047651491494</v>
       </c>
       <c r="K48" t="n">
-        <v>0.112812893274769</v>
+        <v>0.06980095781629543</v>
       </c>
       <c r="L48" t="n">
-        <v>0.4734586201414115</v>
+        <v>0.4919074574683899</v>
       </c>
       <c r="M48" t="n">
-        <v>3.689594567822128</v>
+        <v>3.762510994332883</v>
       </c>
       <c r="N48" t="n">
-        <v>4.336928262298008</v>
+        <v>4.339334064813332</v>
       </c>
       <c r="O48" t="n">
-        <v>0.02559752403332129</v>
+        <v>0.02584743655599214</v>
       </c>
       <c r="P48" t="n">
-        <v>0.03156462700033911</v>
+        <v>0.03165177608440705</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.05520509248539819</v>
+        <v>0.06691184864991848</v>
       </c>
       <c r="R48" t="n">
-        <v>0.03932594497329257</v>
+        <v>0.04004293311549639</v>
       </c>
       <c r="S48" t="n">
-        <v>0.1975976100558738</v>
+        <v>0.1913617279317552</v>
       </c>
       <c r="T48" t="n">
-        <v>0.04776671399339266</v>
+        <v>0.04933607593909337</v>
       </c>
       <c r="U48" t="n">
-        <v>0.06003374000187614</v>
+        <v>0.05933650533204041</v>
       </c>
       <c r="V48" t="n">
-        <v>0.1240898913214311</v>
+        <v>0.1329202056380749</v>
       </c>
       <c r="W48" t="n">
-        <v>0.07346333480786012</v>
+        <v>0.06809056873402429</v>
       </c>
       <c r="X48" t="n">
-        <v>3.650187926655053</v>
+        <v>3.287452784980827</v>
       </c>
     </row>
     <row r="49">
@@ -4331,61 +4331,61 @@
         <v>27.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4784766675558373</v>
+        <v>0.4784766676196412</v>
       </c>
       <c r="G49" t="n">
         <v>0.1167133520074696</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1617722833471003</v>
+        <v>0.1617722832354314</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2200624129180908</v>
+        <v>0.2200624129775048</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02297528417150188</v>
+        <v>0.0229752841599529</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3620994881251263</v>
+        <v>0.3226065171575305</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4642049442610478</v>
+        <v>0.4685201933535184</v>
       </c>
       <c r="M49" t="n">
-        <v>4.033112792883243</v>
+        <v>4.046686012503025</v>
       </c>
       <c r="N49" t="n">
-        <v>4.397384474855732</v>
+        <v>4.395231242972984</v>
       </c>
       <c r="O49" t="n">
-        <v>0.0161874793892966</v>
+        <v>0.01626222066172079</v>
       </c>
       <c r="P49" t="n">
-        <v>0.01009976348879426</v>
+        <v>0.009895613527908272</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.01862565673184269</v>
+        <v>0.01885785546158392</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01790466064962356</v>
+        <v>0.01777161017576374</v>
       </c>
       <c r="S49" t="n">
-        <v>0.09152580202954097</v>
+        <v>0.08762655475589139</v>
       </c>
       <c r="T49" t="n">
-        <v>0.02868247334494153</v>
+        <v>0.02883306571836421</v>
       </c>
       <c r="U49" t="n">
-        <v>0.01449451821969203</v>
+        <v>0.01519620633460224</v>
       </c>
       <c r="V49" t="n">
-        <v>0.04102217925389352</v>
+        <v>0.04258675585440633</v>
       </c>
       <c r="W49" t="n">
-        <v>0.02774209885819313</v>
+        <v>0.02914151221832841</v>
       </c>
       <c r="X49" t="n">
-        <v>0.3134519477737845</v>
+        <v>0.2951193988666913</v>
       </c>
     </row>
     <row r="50">
@@ -4411,61 +4411,61 @@
         <v>22.6</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4707222729765161</v>
+        <v>0.4707222730832482</v>
       </c>
       <c r="G50" t="n">
         <v>0.1404691670178395</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06718571998428063</v>
+        <v>0.06718571980350242</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2979720652205344</v>
+        <v>0.2979720652617544</v>
       </c>
       <c r="J50" t="n">
-        <v>0.02365077480082941</v>
+        <v>0.02365077483365554</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5100697585861687</v>
+        <v>0.4990340157055358</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5539703020498961</v>
+        <v>0.5576546440713213</v>
       </c>
       <c r="M50" t="n">
-        <v>4.291959939524077</v>
+        <v>4.286590071874298</v>
       </c>
       <c r="N50" t="n">
-        <v>4.521509823790423</v>
+        <v>4.457199233417131</v>
       </c>
       <c r="O50" t="n">
-        <v>0.0644694333215249</v>
+        <v>0.06519054081141964</v>
       </c>
       <c r="P50" t="n">
-        <v>0.05991636849154471</v>
+        <v>0.06145302556558209</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.0604794949816118</v>
+        <v>0.0607507902343687</v>
       </c>
       <c r="R50" t="n">
-        <v>0.03297584830203118</v>
+        <v>0.03420241799909936</v>
       </c>
       <c r="S50" t="n">
-        <v>0.004409774390758087</v>
+        <v>0.01150379558953721</v>
       </c>
       <c r="T50" t="n">
-        <v>0.1964375030733685</v>
+        <v>0.2140719229504228</v>
       </c>
       <c r="U50" t="n">
-        <v>0.2170547427926068</v>
+        <v>0.2184813177742955</v>
       </c>
       <c r="V50" t="n">
-        <v>0.2283578671378693</v>
+        <v>0.2209509175972313</v>
       </c>
       <c r="W50" t="n">
-        <v>0.1221695992670814</v>
+        <v>0.1322486686835949</v>
       </c>
       <c r="X50" t="n">
-        <v>25.76750488950472</v>
+        <v>16.25084686193938</v>
       </c>
     </row>
     <row r="51">
@@ -4491,61 +4491,61 @@
         <v>12.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4132915616414226</v>
+        <v>0.4132915619983448</v>
       </c>
       <c r="G51" t="n">
         <v>0.2602133749674733</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02750138666645612</v>
+        <v>0.02750138682641973</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2472592619614906</v>
+        <v>0.247259261508163</v>
       </c>
       <c r="J51" t="n">
-        <v>0.05173441476315732</v>
+        <v>0.05173441469959904</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4766078924922043</v>
+        <v>0.4747357510883822</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5522904382153022</v>
+        <v>0.5586303904736262</v>
       </c>
       <c r="M51" t="n">
-        <v>3.851203782657342</v>
+        <v>3.849426342197498</v>
       </c>
       <c r="N51" t="n">
-        <v>4.429547288090052</v>
+        <v>4.43022679476616</v>
       </c>
       <c r="O51" t="n">
-        <v>0.05426323129579202</v>
+        <v>0.05454904850794997</v>
       </c>
       <c r="P51" t="n">
-        <v>0.04064371055427094</v>
+        <v>0.04120494255466624</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.1267044319482724</v>
+        <v>0.127982663838095</v>
       </c>
       <c r="R51" t="n">
-        <v>0.0629569471919369</v>
+        <v>0.06373674153799248</v>
       </c>
       <c r="S51" t="n">
-        <v>0.2143110993727872</v>
+        <v>0.2175562920146673</v>
       </c>
       <c r="T51" t="n">
-        <v>0.1308918225289418</v>
+        <v>0.1321140241879405</v>
       </c>
       <c r="U51" t="n">
-        <v>0.08068333853008874</v>
+        <v>0.08216689881997412</v>
       </c>
       <c r="V51" t="n">
-        <v>0.2328825484903567</v>
+        <v>0.2283350856669356</v>
       </c>
       <c r="W51" t="n">
-        <v>0.1170864230665695</v>
+        <v>0.1193181342579305</v>
       </c>
       <c r="X51" t="n">
-        <v>2.357640730774623</v>
+        <v>2.407129196586237</v>
       </c>
     </row>
     <row r="52">
@@ -4571,61 +4571,61 @@
         <v>28.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4153806106757402</v>
+        <v>0.4153806106021484</v>
       </c>
       <c r="G52" t="n">
         <v>0.1113895850737956</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3106906626687218</v>
+        <v>0.3106906628036006</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1579071580203451</v>
+        <v>0.1579071579734052</v>
       </c>
       <c r="J52" t="n">
-        <v>0.004631983561397277</v>
+        <v>0.004631983547050241</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1562936953832578</v>
+        <v>0.1003996704124989</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2431379390752078</v>
+        <v>0.1776022826614817</v>
       </c>
       <c r="M52" t="n">
-        <v>4.255272484088167</v>
+        <v>4.241864768630935</v>
       </c>
       <c r="N52" t="n">
-        <v>4.298538256987295</v>
+        <v>4.28178334926914</v>
       </c>
       <c r="O52" t="n">
-        <v>0.008060321128216426</v>
+        <v>0.007696363224374694</v>
       </c>
       <c r="P52" t="n">
-        <v>0.003790983972572807</v>
+        <v>0.003093509744386538</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.008374729883284119</v>
+        <v>0.007832644084126341</v>
       </c>
       <c r="R52" t="n">
-        <v>0.004452670947736255</v>
+        <v>0.003482558159816543</v>
       </c>
       <c r="S52" t="n">
-        <v>0.01360188882076303</v>
+        <v>0.009738484203240635</v>
       </c>
       <c r="T52" t="n">
-        <v>0.0143470719591339</v>
+        <v>0.01397451495751428</v>
       </c>
       <c r="U52" t="n">
-        <v>0.009087880260668903</v>
+        <v>0.008342393898339309</v>
       </c>
       <c r="V52" t="n">
-        <v>0.01671713507210094</v>
+        <v>0.0154960188473149</v>
       </c>
       <c r="W52" t="n">
-        <v>0.0118800269569116</v>
+        <v>0.0106940368772496</v>
       </c>
       <c r="X52" t="n">
-        <v>0.03680078305480584</v>
+        <v>0.03035286461782028</v>
       </c>
     </row>
     <row r="53">
@@ -4651,61 +4651,61 @@
         <v>26.8</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4510893860666219</v>
+        <v>0.4510893861537268</v>
       </c>
       <c r="G53" t="n">
         <v>0.1184553423359393</v>
       </c>
       <c r="H53" t="n">
-        <v>0.200863297038614</v>
+        <v>0.2008632968133135</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2264019040843809</v>
+        <v>0.2264019042000988</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00319007047444387</v>
+        <v>0.003190070496921492</v>
       </c>
       <c r="K53" t="n">
-        <v>0.3358214977156689</v>
+        <v>0.2783551458295477</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2368791358636469</v>
+        <v>0.2433294584670261</v>
       </c>
       <c r="M53" t="n">
-        <v>4.45233489759441</v>
+        <v>4.435198931413451</v>
       </c>
       <c r="N53" t="n">
-        <v>4.414240723809666</v>
+        <v>4.415546712378527</v>
       </c>
       <c r="O53" t="n">
-        <v>0.01770505992205451</v>
+        <v>0.01845554213904164</v>
       </c>
       <c r="P53" t="n">
-        <v>0.009821686894824383</v>
+        <v>0.009212601705791103</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.01035401649560193</v>
+        <v>0.009779086993975726</v>
       </c>
       <c r="R53" t="n">
-        <v>0.02220011370049087</v>
+        <v>0.02092969296106889</v>
       </c>
       <c r="S53" t="n">
-        <v>0.07202129164220857</v>
+        <v>0.0608296337111105</v>
       </c>
       <c r="T53" t="n">
-        <v>0.02974206412240668</v>
+        <v>0.03288668261337075</v>
       </c>
       <c r="U53" t="n">
-        <v>0.01508960660727301</v>
+        <v>0.01444955075999273</v>
       </c>
       <c r="V53" t="n">
-        <v>0.01962137590998968</v>
+        <v>0.01857969413767693</v>
       </c>
       <c r="W53" t="n">
-        <v>0.03754169458747039</v>
+        <v>0.03708161084141964</v>
       </c>
       <c r="X53" t="n">
-        <v>0.09576922539061115</v>
+        <v>0.08422742951966675</v>
       </c>
     </row>
     <row r="54">
@@ -4731,61 +4731,61 @@
         <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4286683890706328</v>
+        <v>0.4286683889482371</v>
       </c>
       <c r="G54" t="n">
         <v>0.1269841269841269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2576179527120835</v>
+        <v>0.2576179529315623</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1597790966902238</v>
+        <v>0.15977909662141</v>
       </c>
       <c r="J54" t="n">
-        <v>0.02695043454293275</v>
+        <v>0.02695043451466368</v>
       </c>
       <c r="K54" t="n">
-        <v>0.2232363824600347</v>
+        <v>0.1652005085621645</v>
       </c>
       <c r="L54" t="n">
-        <v>0.438351402939473</v>
+        <v>0.4251644770650234</v>
       </c>
       <c r="M54" t="n">
-        <v>4.144200181763916</v>
+        <v>4.147708344073652</v>
       </c>
       <c r="N54" t="n">
-        <v>4.316666210315921</v>
+        <v>4.30350362114648</v>
       </c>
       <c r="O54" t="n">
-        <v>0.02028928225939141</v>
+        <v>0.01988971337232071</v>
       </c>
       <c r="P54" t="n">
-        <v>0.007541285606136035</v>
+        <v>0.006871590546431604</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.02327025920945999</v>
+        <v>0.02420750782417868</v>
       </c>
       <c r="R54" t="n">
-        <v>0.009540216235494416</v>
+        <v>0.008636321122728727</v>
       </c>
       <c r="S54" t="n">
-        <v>0.02380575436381814</v>
+        <v>0.02196053609339923</v>
       </c>
       <c r="T54" t="n">
-        <v>0.03922353821965439</v>
+        <v>0.03873810134905034</v>
       </c>
       <c r="U54" t="n">
-        <v>0.01306399661092278</v>
+        <v>0.0131498431421626</v>
       </c>
       <c r="V54" t="n">
-        <v>0.05468647429942235</v>
+        <v>0.05771223906453791</v>
       </c>
       <c r="W54" t="n">
-        <v>0.01816095842314383</v>
+        <v>0.01867699465030327</v>
       </c>
       <c r="X54" t="n">
-        <v>0.0441391381239669</v>
+        <v>0.04224106197842584</v>
       </c>
     </row>
     <row r="55">
@@ -4811,61 +4811,61 @@
         <v>29</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4347068963260962</v>
+        <v>0.4347068963151978</v>
       </c>
       <c r="G55" t="n">
         <v>0.1094690749863163</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2837256736143648</v>
+        <v>0.2837256736186445</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1694315236798098</v>
+        <v>0.1694315237196296</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00266683139341308</v>
+        <v>0.002666831360211718</v>
       </c>
       <c r="K55" t="n">
-        <v>0.196852432134677</v>
+        <v>0.1364807019502954</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4691666266486137</v>
+        <v>0.4788524816569951</v>
       </c>
       <c r="M55" t="n">
-        <v>4.361472218356489</v>
+        <v>4.361516370208551</v>
       </c>
       <c r="N55" t="n">
-        <v>4.402641732322775</v>
+        <v>4.403331791201476</v>
       </c>
       <c r="O55" t="n">
-        <v>0.01512321618874698</v>
+        <v>0.01535412715228182</v>
       </c>
       <c r="P55" t="n">
-        <v>0.008674562808153093</v>
+        <v>0.008608147286653035</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.02961247541669653</v>
+        <v>0.03600947778639862</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01445354587240994</v>
+        <v>0.01444448331432654</v>
       </c>
       <c r="S55" t="n">
-        <v>0.01441899610753118</v>
+        <v>0.01435576842059705</v>
       </c>
       <c r="T55" t="n">
-        <v>0.02662204894152851</v>
+        <v>0.02742936421856233</v>
       </c>
       <c r="U55" t="n">
-        <v>0.01272464416113266</v>
+        <v>0.01265928261410693</v>
       </c>
       <c r="V55" t="n">
-        <v>0.05656063820735676</v>
+        <v>0.06596761746265824</v>
       </c>
       <c r="W55" t="n">
-        <v>0.02038180191819067</v>
+        <v>0.02057914882484339</v>
       </c>
       <c r="X55" t="n">
-        <v>0.02523082379732405</v>
+        <v>0.02469106917293103</v>
       </c>
     </row>
     <row r="56">
@@ -4891,61 +4891,61 @@
         <v>19.9</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3573142119608926</v>
+        <v>0.3573142119374196</v>
       </c>
       <c r="G56" t="n">
         <v>0.1595277977187525</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2647607177751945</v>
+        <v>0.2647607177672366</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1794591218770647</v>
+        <v>0.179459121882217</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03893815066809572</v>
+        <v>0.03893815069437438</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2062853367551514</v>
+        <v>0.150223218442535</v>
       </c>
       <c r="L56" t="n">
-        <v>0.389216721446197</v>
+        <v>0.3808533813344335</v>
       </c>
       <c r="M56" t="n">
-        <v>4.024244761351998</v>
+        <v>4.031079539857037</v>
       </c>
       <c r="N56" t="n">
-        <v>4.337611414464551</v>
+        <v>4.33111338911064</v>
       </c>
       <c r="O56" t="n">
-        <v>0.01393463174913516</v>
+        <v>0.01365934204441689</v>
       </c>
       <c r="P56" t="n">
-        <v>0.007758396099700073</v>
+        <v>0.00732117792901337</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.01799209052484299</v>
+        <v>0.01911815877714705</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01437359240774169</v>
+        <v>0.0135381952528184</v>
       </c>
       <c r="S56" t="n">
-        <v>0.04448511045302854</v>
+        <v>0.04271879795866213</v>
       </c>
       <c r="T56" t="n">
-        <v>0.0254295940444287</v>
+        <v>0.02516393487714456</v>
       </c>
       <c r="U56" t="n">
-        <v>0.01402327458422527</v>
+        <v>0.0139242004093816</v>
       </c>
       <c r="V56" t="n">
-        <v>0.04295491789855975</v>
+        <v>0.04645829957072822</v>
       </c>
       <c r="W56" t="n">
-        <v>0.02516004420962444</v>
+        <v>0.0253620002026916</v>
       </c>
       <c r="X56" t="n">
-        <v>0.1114880976299194</v>
+        <v>0.1080049263837845</v>
       </c>
     </row>
     <row r="57">
@@ -4971,61 +4971,61 @@
         <v>13.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3569988198360919</v>
+        <v>0.3569988198034146</v>
       </c>
       <c r="G57" t="n">
         <v>0.2369106846718786</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1636235303975117</v>
+        <v>0.1636235302919157</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2180246773556286</v>
+        <v>0.2180246774233276</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02444228773888892</v>
+        <v>0.02444228780946331</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3797827501136171</v>
+        <v>0.336114860226541</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4584475774641634</v>
+        <v>0.4552752039430819</v>
       </c>
       <c r="M57" t="n">
-        <v>4.247766393668665</v>
+        <v>4.246456518302081</v>
       </c>
       <c r="N57" t="n">
-        <v>4.374906267354293</v>
+        <v>4.371571953182547</v>
       </c>
       <c r="O57" t="n">
-        <v>0.02048295023548657</v>
+        <v>0.02054016343274672</v>
       </c>
       <c r="P57" t="n">
-        <v>0.008175415431832677</v>
+        <v>0.007959635531833945</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.01662787973941763</v>
+        <v>0.01638030107516865</v>
       </c>
       <c r="R57" t="n">
-        <v>0.01377617510323336</v>
+        <v>0.01336152111759987</v>
       </c>
       <c r="S57" t="n">
-        <v>0.02115101029095347</v>
+        <v>0.02006014406651316</v>
       </c>
       <c r="T57" t="n">
-        <v>0.03926956885353038</v>
+        <v>0.0398681910123069</v>
       </c>
       <c r="U57" t="n">
-        <v>0.01315596784326675</v>
+        <v>0.01308319382815353</v>
       </c>
       <c r="V57" t="n">
-        <v>0.03491681451251267</v>
+        <v>0.03511668678756711</v>
       </c>
       <c r="W57" t="n">
-        <v>0.02011532732068335</v>
+        <v>0.02064630885425539</v>
       </c>
       <c r="X57" t="n">
-        <v>0.03268202368378623</v>
+        <v>0.03206343586212988</v>
       </c>
     </row>
     <row r="58">
@@ -5051,61 +5051,61 @@
         <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3897461385626112</v>
+        <v>0.3897461386008995</v>
       </c>
       <c r="G58" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2557628102080468</v>
+        <v>0.2557628103268892</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2061345128303654</v>
+        <v>0.2061345125957501</v>
       </c>
       <c r="J58" t="n">
-        <v>0.02625641629885448</v>
+        <v>0.02625641637633904</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2238699782819489</v>
+        <v>0.1666120314608137</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5168314759921724</v>
+        <v>0.5098746874725855</v>
       </c>
       <c r="M58" t="n">
-        <v>4.108210897062339</v>
+        <v>4.116850885198406</v>
       </c>
       <c r="N58" t="n">
-        <v>4.432911269152706</v>
+        <v>4.418557517915638</v>
       </c>
       <c r="O58" t="n">
-        <v>0.04290087137624837</v>
+        <v>0.04064248904105216</v>
       </c>
       <c r="P58" t="n">
-        <v>0.00981012262563506</v>
+        <v>0.009468112963776623</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.04896941713079145</v>
+        <v>0.05035695827195752</v>
       </c>
       <c r="R58" t="n">
-        <v>0.009270981699111678</v>
+        <v>0.008645121709449179</v>
       </c>
       <c r="S58" t="n">
-        <v>0.04951899973698004</v>
+        <v>0.04631045476412002</v>
       </c>
       <c r="T58" t="n">
-        <v>0.1030038171473445</v>
+        <v>0.09372273088888684</v>
       </c>
       <c r="U58" t="n">
-        <v>0.01639075170255174</v>
+        <v>0.01523593911997508</v>
       </c>
       <c r="V58" t="n">
-        <v>0.1346258916837078</v>
+        <v>0.1350167328115132</v>
       </c>
       <c r="W58" t="n">
-        <v>0.01830335465022096</v>
+        <v>0.01867766348502505</v>
       </c>
       <c r="X58" t="n">
-        <v>0.105157014485246</v>
+        <v>0.1007749065461759</v>
       </c>
     </row>
     <row r="59">
@@ -5131,61 +5131,61 @@
         <v>10.6506024096385</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4031657915982697</v>
+        <v>0.4031657917179133</v>
       </c>
       <c r="G59" t="n">
         <v>0.2980679451267702</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09858303468278869</v>
+        <v>0.098583034577217</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1793800069532604</v>
+        <v>0.1793800069472718</v>
       </c>
       <c r="J59" t="n">
-        <v>0.02080322163891103</v>
+        <v>0.02080322163082778</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4652114978160279</v>
+        <v>0.4445932488388378</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5160146015280053</v>
+        <v>0.5307886334085006</v>
       </c>
       <c r="M59" t="n">
-        <v>4.189896485281355</v>
+        <v>4.18553294972197</v>
       </c>
       <c r="N59" t="n">
-        <v>4.385968736067589</v>
+        <v>4.387099489018315</v>
       </c>
       <c r="O59" t="n">
-        <v>0.01039003559942345</v>
+        <v>0.01076952506511486</v>
       </c>
       <c r="P59" t="n">
-        <v>0.004090829711645934</v>
+        <v>0.00417709220960882</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.008140012196128747</v>
+        <v>0.007500892399696781</v>
       </c>
       <c r="R59" t="n">
-        <v>0.005967987584729168</v>
+        <v>0.006025281602482127</v>
       </c>
       <c r="S59" t="n">
-        <v>0.00687699182284492</v>
+        <v>0.006865843552493413</v>
       </c>
       <c r="T59" t="n">
-        <v>0.01724182448402028</v>
+        <v>0.01821453852289469</v>
       </c>
       <c r="U59" t="n">
-        <v>0.00502919546687001</v>
+        <v>0.00514879276089495</v>
       </c>
       <c r="V59" t="n">
-        <v>0.01234045870613052</v>
+        <v>0.01108722561313881</v>
       </c>
       <c r="W59" t="n">
-        <v>0.005794323939093651</v>
+        <v>0.005996344815215071</v>
       </c>
       <c r="X59" t="n">
-        <v>0.006484472294282609</v>
+        <v>0.006540979989240953</v>
       </c>
     </row>
     <row r="60">
@@ -5211,61 +5211,61 @@
         <v>45.2784503631961</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6185024514073951</v>
+        <v>0.6185024514128479</v>
       </c>
       <c r="G60" t="n">
         <v>0.07011289364230544</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1901432799511997</v>
+        <v>0.1901432797896153</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1060804578008114</v>
+        <v>0.1060804579527164</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0151609171982884</v>
+        <v>0.015160917202515</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3216419994495925</v>
+        <v>0.271635444752685</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2754910818037129</v>
+        <v>0.2195716630807835</v>
       </c>
       <c r="M60" t="n">
-        <v>4.066724723170381</v>
+        <v>4.049738163537739</v>
       </c>
       <c r="N60" t="n">
-        <v>4.195277617408031</v>
+        <v>4.172347246401958</v>
       </c>
       <c r="O60" t="n">
-        <v>0.002206963725161294</v>
+        <v>0.00241039706945474</v>
       </c>
       <c r="P60" t="n">
-        <v>0.001742623613483473</v>
+        <v>0.001473172287991899</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.001144671944644499</v>
+        <v>0.001046641284367262</v>
       </c>
       <c r="R60" t="n">
-        <v>0.001733827611514837</v>
+        <v>0.001440471365648423</v>
       </c>
       <c r="S60" t="n">
-        <v>0.004802679878084692</v>
+        <v>0.004332077227352854</v>
       </c>
       <c r="T60" t="n">
-        <v>0.003094441657613748</v>
+        <v>0.00343596475182354</v>
       </c>
       <c r="U60" t="n">
-        <v>0.002652182332641902</v>
+        <v>0.002461851165627571</v>
       </c>
       <c r="V60" t="n">
-        <v>0.002224462588535324</v>
+        <v>0.002115391003003984</v>
       </c>
       <c r="W60" t="n">
-        <v>0.00243026684505122</v>
+        <v>0.002248323527566715</v>
       </c>
       <c r="X60" t="n">
-        <v>0.005635145456089533</v>
+        <v>0.005208112915690799</v>
       </c>
     </row>
     <row r="61">
@@ -5291,61 +5291,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G61" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J61" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4036215013039137</v>
+        <v>0.3796724012853681</v>
       </c>
       <c r="L61" t="n">
-        <v>0.3291782936247932</v>
+        <v>0.3390577770844542</v>
       </c>
       <c r="M61" t="n">
-        <v>3.867733074427858</v>
+        <v>3.879317755135752</v>
       </c>
       <c r="N61" t="n">
-        <v>4.235242217482573</v>
+        <v>4.246280826325399</v>
       </c>
       <c r="O61" t="n">
-        <v>0.004447214793646029</v>
+        <v>0.00575316362196893</v>
       </c>
       <c r="P61" t="n">
-        <v>0.00497701255367182</v>
+        <v>0.005062947224215557</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.002702829360422214</v>
+        <v>0.002419944293059719</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01117415245994553</v>
+        <v>0.01119327543085338</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0337429399063176</v>
+        <v>0.03461995564307761</v>
       </c>
       <c r="T61" t="n">
-        <v>0.005325854961655736</v>
+        <v>0.007581458519907268</v>
       </c>
       <c r="U61" t="n">
-        <v>0.006172097738739482</v>
+        <v>0.006690418982808326</v>
       </c>
       <c r="V61" t="n">
-        <v>0.004342154833490982</v>
+        <v>0.003929488534692197</v>
       </c>
       <c r="W61" t="n">
-        <v>0.01086010056984378</v>
+        <v>0.0109269479530494</v>
       </c>
       <c r="X61" t="n">
-        <v>0.1646120359485194</v>
+        <v>0.1723641035415758</v>
       </c>
     </row>
     <row r="62">
@@ -5371,61 +5371,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G62" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I62" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K62" t="n">
-        <v>0.4247196273085029</v>
+        <v>0.3921724768283549</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2038783435409886</v>
+        <v>0.3087502571814861</v>
       </c>
       <c r="M62" t="n">
-        <v>4.224767018744261</v>
+        <v>4.225288773594851</v>
       </c>
       <c r="N62" t="n">
-        <v>4.185384820035271</v>
+        <v>4.220839038480732</v>
       </c>
       <c r="O62" t="n">
-        <v>0.007335816276081557</v>
+        <v>0.007192241703486047</v>
       </c>
       <c r="P62" t="n">
-        <v>0.00177048503927576</v>
+        <v>0.002535635506700245</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.003011739306411712</v>
+        <v>0.002998724069012966</v>
       </c>
       <c r="R62" t="n">
-        <v>0.01893161898719915</v>
+        <v>0.0187154930933048</v>
       </c>
       <c r="S62" t="n">
-        <v>0.01217604160081927</v>
+        <v>0.01197464971498062</v>
       </c>
       <c r="T62" t="n">
-        <v>0.01077351169967527</v>
+        <v>0.01100535342838034</v>
       </c>
       <c r="U62" t="n">
-        <v>0.005049997229193453</v>
+        <v>0.005628353947781804</v>
       </c>
       <c r="V62" t="n">
-        <v>0.004836117657750849</v>
+        <v>0.004792074929892625</v>
       </c>
       <c r="W62" t="n">
-        <v>0.02679462232153719</v>
+        <v>0.02805427960888383</v>
       </c>
       <c r="X62" t="n">
-        <v>0.02356218210591175</v>
+        <v>0.02320576710364456</v>
       </c>
     </row>
     <row r="63">
@@ -5451,61 +5451,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G63" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I63" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J63" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K63" t="n">
-        <v>0.4162108180030814</v>
+        <v>0.3909781496832698</v>
       </c>
       <c r="L63" t="n">
-        <v>0.277130483578434</v>
+        <v>0.3326910491138318</v>
       </c>
       <c r="M63" t="n">
-        <v>3.980345176190739</v>
+        <v>3.987165725813917</v>
       </c>
       <c r="N63" t="n">
-        <v>4.232461252991964</v>
+        <v>4.243966914732664</v>
       </c>
       <c r="O63" t="n">
-        <v>0.005332529023346291</v>
+        <v>0.00579495802472149</v>
       </c>
       <c r="P63" t="n">
-        <v>0.00309157626447355</v>
+        <v>0.003672024362810125</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.002293334024470339</v>
+        <v>0.002229897991891912</v>
       </c>
       <c r="R63" t="n">
-        <v>0.009301363281283675</v>
+        <v>0.009203975306881563</v>
       </c>
       <c r="S63" t="n">
-        <v>0.01915487231474526</v>
+        <v>0.01830185045071924</v>
       </c>
       <c r="T63" t="n">
-        <v>0.00722828356898381</v>
+        <v>0.008211272072931267</v>
       </c>
       <c r="U63" t="n">
-        <v>0.006132585586084572</v>
+        <v>0.006171357247873235</v>
       </c>
       <c r="V63" t="n">
-        <v>0.003609667966790376</v>
+        <v>0.003522971137554023</v>
       </c>
       <c r="W63" t="n">
-        <v>0.009767000185006612</v>
+        <v>0.0102424944787793</v>
       </c>
       <c r="X63" t="n">
-        <v>0.03933828290409942</v>
+        <v>0.03649186218557559</v>
       </c>
     </row>
     <row r="64">
@@ -5531,61 +5531,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G64" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I64" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K64" t="n">
-        <v>0.3718776254920512</v>
+        <v>0.3519822455432539</v>
       </c>
       <c r="L64" t="n">
-        <v>0.3314611134802327</v>
+        <v>0.3747703089563006</v>
       </c>
       <c r="M64" t="n">
-        <v>3.731272522811424</v>
+        <v>3.818864310595396</v>
       </c>
       <c r="N64" t="n">
-        <v>4.242970261425485</v>
+        <v>4.257228695506939</v>
       </c>
       <c r="O64" t="n">
-        <v>0.005415604988936358</v>
+        <v>0.00572896742969062</v>
       </c>
       <c r="P64" t="n">
-        <v>0.004456283058070487</v>
+        <v>0.004763010294998852</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.004068817441642249</v>
+        <v>0.003874281575703709</v>
       </c>
       <c r="R64" t="n">
-        <v>0.01982482513235766</v>
+        <v>0.01958406944348003</v>
       </c>
       <c r="S64" t="n">
-        <v>0.05636550849338188</v>
+        <v>0.04803510960340063</v>
       </c>
       <c r="T64" t="n">
-        <v>0.007703026881927051</v>
+        <v>0.00813999374186143</v>
       </c>
       <c r="U64" t="n">
-        <v>0.006781574498109944</v>
+        <v>0.00699760039780106</v>
       </c>
       <c r="V64" t="n">
-        <v>0.006430308932345953</v>
+        <v>0.006235106687557687</v>
       </c>
       <c r="W64" t="n">
-        <v>0.02905749399509015</v>
+        <v>0.03015220670694218</v>
       </c>
       <c r="X64" t="n">
-        <v>0.889839390409737</v>
+        <v>0.5738232753036951</v>
       </c>
     </row>
     <row r="65">
@@ -5611,61 +5611,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G65" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I65" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4080876425054237</v>
+        <v>0.3840299639288887</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3821976196902763</v>
+        <v>0.409896142652755</v>
       </c>
       <c r="M65" t="n">
-        <v>3.907692534421139</v>
+        <v>3.920894528082243</v>
       </c>
       <c r="N65" t="n">
-        <v>4.267407857471007</v>
+        <v>4.277772107866112</v>
       </c>
       <c r="O65" t="n">
-        <v>0.005694069250824849</v>
+        <v>0.006362949212798998</v>
       </c>
       <c r="P65" t="n">
-        <v>0.005911656708783651</v>
+        <v>0.006054999645566156</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.004569454280181507</v>
+        <v>0.00424163918838528</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01174523859127137</v>
+        <v>0.01171801657236894</v>
       </c>
       <c r="S65" t="n">
-        <v>0.03453122663648231</v>
+        <v>0.033231601681557</v>
       </c>
       <c r="T65" t="n">
-        <v>0.007175759003153996</v>
+        <v>0.008210353185849204</v>
       </c>
       <c r="U65" t="n">
-        <v>0.00857934600590113</v>
+        <v>0.008999390369542833</v>
       </c>
       <c r="V65" t="n">
-        <v>0.007198438279431697</v>
+        <v>0.006891374876706696</v>
       </c>
       <c r="W65" t="n">
-        <v>0.01201975980910411</v>
+        <v>0.01302461919593224</v>
       </c>
       <c r="X65" t="n">
-        <v>0.1417498947852362</v>
+        <v>0.1303456404869559</v>
       </c>
     </row>
     <row r="66">
@@ -5691,61 +5691,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G66" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J66" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K66" t="n">
-        <v>0.3968412713764273</v>
+        <v>0.3675100802954002</v>
       </c>
       <c r="L66" t="n">
-        <v>0.3258956814720437</v>
+        <v>0.3622485455126082</v>
       </c>
       <c r="M66" t="n">
-        <v>3.964603776049459</v>
+        <v>3.976012601874739</v>
       </c>
       <c r="N66" t="n">
-        <v>4.242096069367671</v>
+        <v>4.255327772188516</v>
       </c>
       <c r="O66" t="n">
-        <v>0.005379639451384995</v>
+        <v>0.00588459785496899</v>
       </c>
       <c r="P66" t="n">
-        <v>0.004799924413841241</v>
+        <v>0.004948105293628108</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.003969791877362047</v>
+        <v>0.003703019694867113</v>
       </c>
       <c r="R66" t="n">
-        <v>0.01743409117818958</v>
+        <v>0.01706086942439798</v>
       </c>
       <c r="S66" t="n">
-        <v>0.03171804094818882</v>
+        <v>0.0301752561198795</v>
       </c>
       <c r="T66" t="n">
-        <v>0.007488137571749349</v>
+        <v>0.008352033505711532</v>
       </c>
       <c r="U66" t="n">
-        <v>0.006955814879052309</v>
+        <v>0.007099879358188993</v>
       </c>
       <c r="V66" t="n">
-        <v>0.006338979634622432</v>
+        <v>0.006038785012255546</v>
       </c>
       <c r="W66" t="n">
-        <v>0.02328861869333015</v>
+        <v>0.023968077440724</v>
       </c>
       <c r="X66" t="n">
-        <v>0.1740360039193189</v>
+        <v>0.1546701015000718</v>
       </c>
     </row>
     <row r="67">
@@ -5771,61 +5771,61 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G67" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4211240356731683</v>
+        <v>0.3803330682882993</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3997137698529541</v>
+        <v>0.4020406949830687</v>
       </c>
       <c r="M67" t="n">
-        <v>4.407889787316897</v>
+        <v>4.396081402485587</v>
       </c>
       <c r="N67" t="n">
-        <v>4.344915471796567</v>
+        <v>4.340081690395644</v>
       </c>
       <c r="O67" t="n">
-        <v>0.004182986571473168</v>
+        <v>0.00470597493627709</v>
       </c>
       <c r="P67" t="n">
-        <v>0.01078621694386006</v>
+        <v>0.01089284479685998</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.00430956785338889</v>
+        <v>0.004340232063528248</v>
       </c>
       <c r="R67" t="n">
-        <v>0.009340045245044741</v>
+        <v>0.009832837639233902</v>
       </c>
       <c r="S67" t="n">
-        <v>0.05333489483130417</v>
+        <v>0.05410323472967622</v>
       </c>
       <c r="T67" t="n">
-        <v>0.005675132658984882</v>
+        <v>0.006130955211817612</v>
       </c>
       <c r="U67" t="n">
-        <v>0.01133921166057252</v>
+        <v>0.01212971166427852</v>
       </c>
       <c r="V67" t="n">
-        <v>0.009639497765579491</v>
+        <v>0.009864172910482291</v>
       </c>
       <c r="W67" t="n">
-        <v>0.0130696505554789</v>
+        <v>0.01475544444374965</v>
       </c>
       <c r="X67" t="n">
-        <v>0.07959727253584052</v>
+        <v>0.08605202936124631</v>
       </c>
     </row>
     <row r="68">
@@ -5851,61 +5851,61 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G68" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4316687937084649</v>
+        <v>0.3898978456369452</v>
       </c>
       <c r="L68" t="n">
-        <v>0.41649734086178</v>
+        <v>0.4270616471564336</v>
       </c>
       <c r="M68" t="n">
-        <v>4.511522348131344</v>
+        <v>4.499873541330101</v>
       </c>
       <c r="N68" t="n">
-        <v>4.351448479696841</v>
+        <v>4.347553934066302</v>
       </c>
       <c r="O68" t="n">
-        <v>0.00424138894137788</v>
+        <v>0.004756247585380413</v>
       </c>
       <c r="P68" t="n">
-        <v>0.01293400812612018</v>
+        <v>0.01303020923466366</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.005306252108714812</v>
+        <v>0.005216868187635153</v>
       </c>
       <c r="R68" t="n">
-        <v>0.01417652653712615</v>
+        <v>0.01487230500291858</v>
       </c>
       <c r="S68" t="n">
-        <v>0.01674155348745422</v>
+        <v>0.01695949343563309</v>
       </c>
       <c r="T68" t="n">
-        <v>0.006671833150905393</v>
+        <v>0.007269573840837172</v>
       </c>
       <c r="U68" t="n">
-        <v>0.01251769926347516</v>
+        <v>0.01304481678556396</v>
       </c>
       <c r="V68" t="n">
-        <v>0.009177833583778751</v>
+        <v>0.009115431926335764</v>
       </c>
       <c r="W68" t="n">
-        <v>0.02008302323699946</v>
+        <v>0.0224607121293263</v>
       </c>
       <c r="X68" t="n">
-        <v>0.02579373413077969</v>
+        <v>0.02689816682237356</v>
       </c>
     </row>
     <row r="69">
@@ -5931,61 +5931,61 @@
         <v>51.72972972972973</v>
       </c>
       <c r="F69" t="n">
-        <v>0.387003570840844</v>
+        <v>0.3870035708733858</v>
       </c>
       <c r="G69" t="n">
         <v>0.06136902688626825</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3121616657195941</v>
+        <v>0.3121616658061397</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1933504308693656</v>
+        <v>0.1933504307114432</v>
       </c>
       <c r="J69" t="n">
-        <v>0.04611530568392795</v>
+        <v>0.04611530572276303</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1562554941398336</v>
+        <v>0.1000285343957928</v>
       </c>
       <c r="L69" t="n">
-        <v>0.1860927984975772</v>
+        <v>0.1376000214334877</v>
       </c>
       <c r="M69" t="n">
-        <v>4.301187016990272</v>
+        <v>4.290484453614669</v>
       </c>
       <c r="N69" t="n">
-        <v>4.30472981637424</v>
+        <v>4.295072858247461</v>
       </c>
       <c r="O69" t="n">
-        <v>0.003147097540272044</v>
+        <v>0.003000854791929909</v>
       </c>
       <c r="P69" t="n">
-        <v>0.001787254331327555</v>
+        <v>0.001346483925043478</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.003355989857698644</v>
+        <v>0.003286974794902867</v>
       </c>
       <c r="R69" t="n">
-        <v>0.004151462438695826</v>
+        <v>0.003729024982253798</v>
       </c>
       <c r="S69" t="n">
-        <v>0.004066177963885829</v>
+        <v>0.003821443496813115</v>
       </c>
       <c r="T69" t="n">
-        <v>0.004658453729440157</v>
+        <v>0.00455663186683214</v>
       </c>
       <c r="U69" t="n">
-        <v>0.00382052070407284</v>
+        <v>0.003480099302038897</v>
       </c>
       <c r="V69" t="n">
-        <v>0.005374830332393775</v>
+        <v>0.005260231433774976</v>
       </c>
       <c r="W69" t="n">
-        <v>0.005764728644690899</v>
+        <v>0.005413433092642136</v>
       </c>
       <c r="X69" t="n">
-        <v>0.005969957525782609</v>
+        <v>0.005747973998744538</v>
       </c>
     </row>
     <row r="70">
@@ -6011,61 +6011,61 @@
         <v>33.0828025477707</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3260336956980185</v>
+        <v>0.3260336958414495</v>
       </c>
       <c r="G70" t="n">
         <v>0.09595931813875594</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3161491466910983</v>
+        <v>0.31614914647049</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2279586239396759</v>
+        <v>0.2279586239311767</v>
       </c>
       <c r="J70" t="n">
-        <v>0.03389921553245138</v>
+        <v>0.03389921561812766</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1527928836483235</v>
+        <v>0.09682343377553043</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2675350130412292</v>
+        <v>0.2153981185090495</v>
       </c>
       <c r="M70" t="n">
-        <v>4.339893559122465</v>
+        <v>4.334140788598515</v>
       </c>
       <c r="N70" t="n">
-        <v>4.373251304488082</v>
+        <v>4.365335808887848</v>
       </c>
       <c r="O70" t="n">
-        <v>0.003165967423396112</v>
+        <v>0.002981635823612692</v>
       </c>
       <c r="P70" t="n">
-        <v>0.004372072966960185</v>
+        <v>0.003850443757139979</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.005283893054565157</v>
+        <v>0.005119300208277374</v>
       </c>
       <c r="R70" t="n">
-        <v>0.004428065283830173</v>
+        <v>0.003961724875650768</v>
       </c>
       <c r="S70" t="n">
-        <v>0.006206679560439163</v>
+        <v>0.005677537951407735</v>
       </c>
       <c r="T70" t="n">
-        <v>0.004753275643539136</v>
+        <v>0.004592007203264247</v>
       </c>
       <c r="U70" t="n">
-        <v>0.00619426940811917</v>
+        <v>0.005708048298495366</v>
       </c>
       <c r="V70" t="n">
-        <v>0.008463398056181534</v>
+        <v>0.008127003950181459</v>
       </c>
       <c r="W70" t="n">
-        <v>0.00631830776301017</v>
+        <v>0.005875808570249327</v>
       </c>
       <c r="X70" t="n">
-        <v>0.009200714701752901</v>
+        <v>0.008562651143368415</v>
       </c>
     </row>
     <row r="71">
@@ -6091,61 +6091,61 @@
         <v>47.07964601769911</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3936990724378037</v>
+        <v>0.3936990724969831</v>
       </c>
       <c r="G71" t="n">
         <v>0.06743048096431555</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2058669949880412</v>
+        <v>0.2058669949713333</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3043928180016056</v>
+        <v>0.3043928180135104</v>
       </c>
       <c r="J71" t="n">
-        <v>0.02861063360823382</v>
+        <v>0.02861063355385755</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3251980729523765</v>
+        <v>0.2678404883365064</v>
       </c>
       <c r="L71" t="n">
-        <v>0.3388589876391399</v>
+        <v>0.3051587634990652</v>
       </c>
       <c r="M71" t="n">
-        <v>4.4265321563301</v>
+        <v>4.421523566309154</v>
       </c>
       <c r="N71" t="n">
-        <v>4.442666397514478</v>
+        <v>4.440388733304707</v>
       </c>
       <c r="O71" t="n">
-        <v>0.005277935297569794</v>
+        <v>0.005065558036480573</v>
       </c>
       <c r="P71" t="n">
-        <v>0.005565805100206977</v>
+        <v>0.004884855766831945</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.004441519107726513</v>
+        <v>0.004275641635832553</v>
       </c>
       <c r="R71" t="n">
-        <v>0.005146268087504469</v>
+        <v>0.004741783479295108</v>
       </c>
       <c r="S71" t="n">
-        <v>0.005461030654635993</v>
+        <v>0.004989349104461792</v>
       </c>
       <c r="T71" t="n">
-        <v>0.007132163714276796</v>
+        <v>0.006951811543738206</v>
       </c>
       <c r="U71" t="n">
-        <v>0.006783785402912829</v>
+        <v>0.006458311425929288</v>
       </c>
       <c r="V71" t="n">
-        <v>0.007071806517176626</v>
+        <v>0.006873950893965383</v>
       </c>
       <c r="W71" t="n">
-        <v>0.006751666224067892</v>
+        <v>0.006495181441447646</v>
       </c>
       <c r="X71" t="n">
-        <v>0.006713147737019296</v>
+        <v>0.006409392042060496</v>
       </c>
     </row>
     <row r="72">
@@ -6171,61 +6171,61 @@
         <v>37.36805555555556</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2796444532400447</v>
+        <v>0.279644453194911</v>
       </c>
       <c r="G72" t="n">
         <v>0.08495500039822655</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2106458171229023</v>
+        <v>0.2106458171994461</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3902452407206423</v>
+        <v>0.3902452407095023</v>
       </c>
       <c r="J72" t="n">
-        <v>0.03450948851818413</v>
+        <v>0.03450948849791399</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3226988012903637</v>
+        <v>0.2638017802804687</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4018753830295776</v>
+        <v>0.364729337507692</v>
       </c>
       <c r="M72" t="n">
-        <v>4.500658295365612</v>
+        <v>4.502235920367876</v>
       </c>
       <c r="N72" t="n">
-        <v>4.513339304972173</v>
+        <v>4.516127637642509</v>
       </c>
       <c r="O72" t="n">
-        <v>0.004231058406856252</v>
+        <v>0.003969755522468583</v>
       </c>
       <c r="P72" t="n">
-        <v>0.004785879916527147</v>
+        <v>0.00422008676448486</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.005253704867672498</v>
+        <v>0.00495204330355547</v>
       </c>
       <c r="R72" t="n">
-        <v>0.004367304499079646</v>
+        <v>0.004049915939384633</v>
       </c>
       <c r="S72" t="n">
-        <v>0.005890369754721588</v>
+        <v>0.005418125503918425</v>
       </c>
       <c r="T72" t="n">
-        <v>0.005824758281389274</v>
+        <v>0.005612187405771381</v>
       </c>
       <c r="U72" t="n">
-        <v>0.006074366549045653</v>
+        <v>0.005849065215089401</v>
       </c>
       <c r="V72" t="n">
-        <v>0.008329419341902284</v>
+        <v>0.007913218039512695</v>
       </c>
       <c r="W72" t="n">
-        <v>0.006106363786393072</v>
+        <v>0.005815827053809632</v>
       </c>
       <c r="X72" t="n">
-        <v>0.007480121202695747</v>
+        <v>0.007148831460690586</v>
       </c>
     </row>
     <row r="73">
@@ -6251,61 +6251,61 @@
         <v>80.48333333333333</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4426967929782777</v>
+        <v>0.4426967930157429</v>
       </c>
       <c r="G73" t="n">
         <v>0.03944423078819433</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3881444762932012</v>
+        <v>0.388144476200794</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1098624187784432</v>
+        <v>0.1098624188419678</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01985208116188355</v>
+        <v>0.01985208115330091</v>
       </c>
       <c r="K73" t="n">
-        <v>0.08013831924157824</v>
+        <v>0.04031370470886774</v>
       </c>
       <c r="L73" t="n">
-        <v>0.08702574501572126</v>
+        <v>0.05057463727087248</v>
       </c>
       <c r="M73" t="n">
-        <v>4.345718815687934</v>
+        <v>4.339334217678624</v>
       </c>
       <c r="N73" t="n">
-        <v>4.333874464361721</v>
+        <v>4.329509570304954</v>
       </c>
       <c r="O73" t="n">
-        <v>0.001888412387306788</v>
+        <v>0.001836585192314117</v>
       </c>
       <c r="P73" t="n">
-        <v>0.001903126853500366</v>
+        <v>0.001545488128958874</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.00195296573515502</v>
+        <v>0.001936053547121294</v>
       </c>
       <c r="R73" t="n">
-        <v>0.002562615128020493</v>
+        <v>0.002281901664524221</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003918587697836979</v>
+        <v>0.0002467729905005936</v>
       </c>
       <c r="T73" t="n">
-        <v>0.003426901248061201</v>
+        <v>0.003405342874213335</v>
       </c>
       <c r="U73" t="n">
-        <v>0.003470077266613913</v>
+        <v>0.003173086012973959</v>
       </c>
       <c r="V73" t="n">
-        <v>0.00361237224862</v>
+        <v>0.003581983080541543</v>
       </c>
       <c r="W73" t="n">
-        <v>0.004173805820527341</v>
+        <v>0.00396371017291886</v>
       </c>
       <c r="X73" t="n">
-        <v>0.00323384608921796</v>
+        <v>0.003149432981276837</v>
       </c>
     </row>
     <row r="74">
@@ -6331,61 +6331,61 @@
         <v>59.11538461538462</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2579745442485045</v>
+        <v>0.2579745444344787</v>
       </c>
       <c r="G74" t="n">
         <v>0.05370181037064575</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3841123147856094</v>
+        <v>0.384112314707</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2682526027331976</v>
+        <v>0.2682526026085332</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03595872786204279</v>
+        <v>0.0359587278793424</v>
       </c>
       <c r="K74" t="n">
-        <v>0.08375853066839459</v>
+        <v>0.04276213165574472</v>
       </c>
       <c r="L74" t="n">
-        <v>0.1528526074727222</v>
+        <v>0.1025681890668143</v>
       </c>
       <c r="M74" t="n">
-        <v>4.36397608937349</v>
+        <v>4.360056444564394</v>
       </c>
       <c r="N74" t="n">
-        <v>4.403552325235742</v>
+        <v>4.399201030373263</v>
       </c>
       <c r="O74" t="n">
-        <v>0.001606312086320778</v>
+        <v>0.001497351395801339</v>
       </c>
       <c r="P74" t="n">
-        <v>0.002184713787554933</v>
+        <v>0.001776249493755885</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.003201077289766507</v>
+        <v>0.003159015516955978</v>
       </c>
       <c r="R74" t="n">
-        <v>0.002085950472454285</v>
+        <v>0.001906168912111457</v>
       </c>
       <c r="S74" t="n">
-        <v>0.003661090827597367</v>
+        <v>0.003449722675139116</v>
       </c>
       <c r="T74" t="n">
-        <v>0.00334045434321676</v>
+        <v>0.003265495696220424</v>
       </c>
       <c r="U74" t="n">
-        <v>0.003888931906313519</v>
+        <v>0.003488259989089588</v>
       </c>
       <c r="V74" t="n">
-        <v>0.005110530719851648</v>
+        <v>0.005034623689590515</v>
       </c>
       <c r="W74" t="n">
-        <v>0.003644334489883528</v>
+        <v>0.003493287706347263</v>
       </c>
       <c r="X74" t="n">
-        <v>0.005529292580106506</v>
+        <v>0.005338426031883264</v>
       </c>
     </row>
     <row r="75">
@@ -6411,61 +6411,61 @@
         <v>38.49019607843137</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3797999037751007</v>
+        <v>0.379799903884584</v>
       </c>
       <c r="G75" t="n">
         <v>0.0824782281735924</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2705342292388105</v>
+        <v>0.2705342288932795</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2132258416518971</v>
+        <v>0.2132258419102607</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05396179716059933</v>
+        <v>0.05396179713828334</v>
       </c>
       <c r="K75" t="n">
-        <v>0.2067664206129807</v>
+        <v>0.1476874036969633</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2624464874838576</v>
+        <v>0.2169097766187445</v>
       </c>
       <c r="M75" t="n">
-        <v>4.184661703848845</v>
+        <v>4.171047640784607</v>
       </c>
       <c r="N75" t="n">
-        <v>4.2908519767349</v>
+        <v>4.278071179177773</v>
       </c>
       <c r="O75" t="n">
-        <v>0.002886235977613058</v>
+        <v>0.002750447192406759</v>
       </c>
       <c r="P75" t="n">
-        <v>0.004487339328524661</v>
+        <v>0.003952612232653929</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.004028529442128123</v>
+        <v>0.003921053776456239</v>
       </c>
       <c r="R75" t="n">
-        <v>0.00473031133853227</v>
+        <v>0.004291608435658732</v>
       </c>
       <c r="S75" t="n">
-        <v>0.007146110922988586</v>
+        <v>0.006818495129827107</v>
       </c>
       <c r="T75" t="n">
-        <v>0.004392805883387863</v>
+        <v>0.004283318148060207</v>
       </c>
       <c r="U75" t="n">
-        <v>0.005968410581595977</v>
+        <v>0.005536910583288933</v>
       </c>
       <c r="V75" t="n">
-        <v>0.006396828988319664</v>
+        <v>0.006228825851268639</v>
       </c>
       <c r="W75" t="n">
-        <v>0.006426465169334155</v>
+        <v>0.00608260747422677</v>
       </c>
       <c r="X75" t="n">
-        <v>0.01080740736083336</v>
+        <v>0.01043509687905746</v>
       </c>
     </row>
     <row r="76">
@@ -6491,61 +6491,61 @@
         <v>67.76923076923077</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3107335005383793</v>
+        <v>0.3107335004737291</v>
       </c>
       <c r="G76" t="n">
         <v>0.04684431472172675</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5076173756922413</v>
+        <v>0.5076173757282579</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1034441405229936</v>
+        <v>0.1034441405920671</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03136066852465918</v>
+        <v>0.03136066848421915</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02041481449548191</v>
+        <v>0.006316940755609539</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02255561574794553</v>
+        <v>0.008479839422888345</v>
       </c>
       <c r="M76" t="n">
-        <v>4.335730785167194</v>
+        <v>4.333353832661424</v>
       </c>
       <c r="N76" t="n">
-        <v>4.319303662095504</v>
+        <v>4.317490078028524</v>
       </c>
       <c r="O76" t="n">
-        <v>0.00193138604073707</v>
+        <v>0.0019048094539966</v>
       </c>
       <c r="P76" t="n">
-        <v>0.001206419819451297</v>
+        <v>0.001105329039509073</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.001943079122286904</v>
+        <v>0.001942535760760942</v>
       </c>
       <c r="R76" t="n">
-        <v>0.002220330720090912</v>
+        <v>0.002111653341818055</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0007935819215516187</v>
+        <v>0.0007572342869350446</v>
       </c>
       <c r="T76" t="n">
-        <v>0.003560047100253156</v>
+        <v>0.003555241699748322</v>
       </c>
       <c r="U76" t="n">
-        <v>0.002858746704015702</v>
+        <v>0.002807197363610444</v>
       </c>
       <c r="V76" t="n">
-        <v>0.00358430663273694</v>
+        <v>0.003576309549742578</v>
       </c>
       <c r="W76" t="n">
-        <v>0.003747183649823626</v>
+        <v>0.003689721161253848</v>
       </c>
       <c r="X76" t="n">
-        <v>0.002698712607651203</v>
+        <v>0.002685457593809299</v>
       </c>
     </row>
     <row r="77">
@@ -6571,61 +6571,61 @@
         <v>84.83333333333333</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2190992506065154</v>
+        <v>0.2190992505888929</v>
       </c>
       <c r="G77" t="n">
         <v>0.03742164842361306</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4560940070375605</v>
+        <v>0.4560940072232207</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2593330805653106</v>
+        <v>0.2593330804892675</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02805201336700053</v>
+        <v>0.02805201327500588</v>
       </c>
       <c r="K77" t="n">
-        <v>0.0375161600995857</v>
+        <v>0.01454057165154276</v>
       </c>
       <c r="L77" t="n">
-        <v>0.09091298140267795</v>
+        <v>0.05104071392674532</v>
       </c>
       <c r="M77" t="n">
-        <v>4.235925950677315</v>
+        <v>4.230706129780605</v>
       </c>
       <c r="N77" t="n">
-        <v>4.251760422935557</v>
+        <v>4.241902354927587</v>
       </c>
       <c r="O77" t="n">
-        <v>0.001790754486881807</v>
+        <v>0.001728579813357431</v>
       </c>
       <c r="P77" t="n">
-        <v>0.0005576038270875812</v>
+        <v>0.0003318260811728798</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.0022377454173005</v>
+        <v>0.002216589733130873</v>
       </c>
       <c r="R77" t="n">
-        <v>0.0003472352486419925</v>
+        <v>0.0002815277239335915</v>
       </c>
       <c r="S77" t="n">
-        <v>0.001774568129447606</v>
+        <v>0.001675355746545451</v>
       </c>
       <c r="T77" t="n">
-        <v>0.002810193921065609</v>
+        <v>0.002776187633144704</v>
       </c>
       <c r="U77" t="n">
-        <v>0.001984966423812922</v>
+        <v>0.001776660370824875</v>
       </c>
       <c r="V77" t="n">
-        <v>0.003305775828502809</v>
+        <v>0.003273020895314783</v>
       </c>
       <c r="W77" t="n">
-        <v>0.002013132349266835</v>
+        <v>0.001962948714231</v>
       </c>
       <c r="X77" t="n">
-        <v>0.002768444124214075</v>
+        <v>0.002704279506017001</v>
       </c>
     </row>
     <row r="78">
@@ -6651,61 +6651,61 @@
         <v>194.7286349979082</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1878797147510616</v>
+        <v>0.1878797146293589</v>
       </c>
       <c r="G78" t="n">
         <v>0.01630270337301587</v>
       </c>
       <c r="H78" t="n">
-        <v>0.486383629371598</v>
+        <v>0.48638362926571</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2989072313345766</v>
+        <v>0.2989072315377535</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01052672116974796</v>
+        <v>0.01052672119416169</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02699802811307632</v>
+        <v>0.009175722573668135</v>
       </c>
       <c r="L78" t="n">
-        <v>0.07884453720528377</v>
+        <v>0.04320188478660273</v>
       </c>
       <c r="M78" t="n">
-        <v>4.377810298060794</v>
+        <v>4.366330804420246</v>
       </c>
       <c r="N78" t="n">
-        <v>4.386199663350345</v>
+        <v>4.369076403133636</v>
       </c>
       <c r="O78" t="n">
-        <v>0.000771433786867778</v>
+        <v>0.0007203392633440642</v>
       </c>
       <c r="P78" t="n">
-        <v>1.000000000006614e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.00186954059648756</v>
+        <v>0.001914066894694201</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0001599966328199954</v>
+        <v>0.00011006026955287</v>
       </c>
       <c r="S78" t="n">
-        <v>1.000000000001471e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="T78" t="n">
-        <v>0.002042032089348669</v>
+        <v>0.002009510143615828</v>
       </c>
       <c r="U78" t="n">
-        <v>0.002340233760396255</v>
+        <v>0.002280258950356349</v>
       </c>
       <c r="V78" t="n">
-        <v>0.00295903386307918</v>
+        <v>0.003004821614199075</v>
       </c>
       <c r="W78" t="n">
-        <v>0.001703448986633627</v>
+        <v>0.00166135625112434</v>
       </c>
       <c r="X78" t="n">
-        <v>0.002928232256476276</v>
+        <v>0.00302015018658533</v>
       </c>
     </row>
     <row r="79">
@@ -6725,67 +6725,67 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E79" t="n">
         <v>46.1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5078749311749362</v>
+        <v>0.507874931382013</v>
       </c>
       <c r="G79" t="n">
         <v>0.06886340942740074</v>
       </c>
       <c r="H79" t="n">
-        <v>0.224536369038535</v>
+        <v>0.2245363687099741</v>
       </c>
       <c r="I79" t="n">
-        <v>0.198725290359128</v>
+        <v>0.1987252904806123</v>
       </c>
       <c r="J79" t="n">
-        <v>3.234988232153624e-17</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2887378674060793</v>
+        <v>0.2286775418539777</v>
       </c>
       <c r="L79" t="n">
-        <v>0.28961502997839</v>
+        <v>0.2476984005019057</v>
       </c>
       <c r="M79" t="n">
-        <v>4.358789254115512</v>
+        <v>4.343239893866217</v>
       </c>
       <c r="N79" t="n">
-        <v>4.385205411533307</v>
+        <v>4.418846948554335</v>
       </c>
       <c r="O79" t="n">
-        <v>0.001792394564382161</v>
+        <v>0.001716670584802468</v>
       </c>
       <c r="P79" t="n">
-        <v>0.0009492857379808609</v>
+        <v>0.0007701143652709886</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.001301995940293981</v>
+        <v>0.001254266560138549</v>
       </c>
       <c r="R79" t="n">
-        <v>0.001564506408444912</v>
+        <v>0.001377094527512765</v>
       </c>
       <c r="S79" t="n">
-        <v>0.009529623992513012</v>
+        <v>1.000000000000728e-05</v>
       </c>
       <c r="T79" t="n">
-        <v>0.003035577471188402</v>
+        <v>0.002486272629361943</v>
       </c>
       <c r="U79" t="n">
-        <v>0.002106800586566564</v>
+        <v>0.00178425523747522</v>
       </c>
       <c r="V79" t="n">
-        <v>0.002389004431315216</v>
+        <v>0.002214018072321555</v>
       </c>
       <c r="W79" t="n">
-        <v>0.002821008819136486</v>
+        <v>0.002289673483783877</v>
       </c>
       <c r="X79" t="n">
-        <v>5.015224827991929</v>
+        <v>0.1469243680567952</v>
       </c>
     </row>
     <row r="80">
@@ -6805,67 +6805,67 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E80" t="n">
         <v>45.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3936300671811785</v>
+        <v>0.3936300668840204</v>
       </c>
       <c r="G80" t="n">
         <v>0.07039031429275332</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3139495076888332</v>
+        <v>0.3139495080876725</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2220301108372348</v>
+        <v>0.2220301107355537</v>
       </c>
       <c r="J80" t="n">
-        <v>7.592549229303372e-17</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1595546651660966</v>
+        <v>0.1016218464044198</v>
       </c>
       <c r="L80" t="n">
-        <v>0.1839705127100605</v>
+        <v>0.1430862701634006</v>
       </c>
       <c r="M80" t="n">
-        <v>4.445589518440741</v>
+        <v>4.434521093329462</v>
       </c>
       <c r="N80" t="n">
-        <v>4.445854714247583</v>
+        <v>4.467861836396736</v>
       </c>
       <c r="O80" t="n">
-        <v>0.001741258144423309</v>
+        <v>0.001655689360379024</v>
       </c>
       <c r="P80" t="n">
-        <v>0.000902511070875906</v>
+        <v>0.0007463871485078611</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.001485145156700666</v>
+        <v>0.001468015198936214</v>
       </c>
       <c r="R80" t="n">
-        <v>0.001607554423224526</v>
+        <v>0.001444718356091695</v>
       </c>
       <c r="S80" t="n">
-        <v>0.01487261190742616</v>
+        <v>1e-05</v>
       </c>
       <c r="T80" t="n">
-        <v>0.003006286497113137</v>
+        <v>0.002489444800012601</v>
       </c>
       <c r="U80" t="n">
-        <v>0.002178201951364682</v>
+        <v>0.001759367660175774</v>
       </c>
       <c r="V80" t="n">
-        <v>0.002697625817352292</v>
+        <v>0.002537923023799295</v>
       </c>
       <c r="W80" t="n">
-        <v>0.003031547052324913</v>
+        <v>0.002377849083120291</v>
       </c>
       <c r="X80" t="n">
-        <v>18.92836611507056</v>
+        <v>0.2709381883772328</v>
       </c>
     </row>
     <row r="81">
@@ -6885,67 +6885,67 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E81" t="n">
         <v>53.2</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3868686426861032</v>
+        <v>0.386868642759827</v>
       </c>
       <c r="G81" t="n">
         <v>0.05967299200381906</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2367160880230922</v>
+        <v>0.2367160880153139</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3167422772869857</v>
+        <v>0.3167422772210401</v>
       </c>
       <c r="J81" t="n">
-        <v>9.901399624920571e-18</v>
+        <v>1.098340305577317e-17</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2823340712299195</v>
+        <v>0.2184603167025097</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2468016288310105</v>
+        <v>0.2074917496047663</v>
       </c>
       <c r="M81" t="n">
-        <v>4.565156125183966</v>
+        <v>4.558610094916371</v>
       </c>
       <c r="N81" t="n">
-        <v>4.555278021507538</v>
+        <v>4.54292419943042</v>
       </c>
       <c r="O81" t="n">
-        <v>0.001753349897503287</v>
+        <v>0.001682203720916945</v>
       </c>
       <c r="P81" t="n">
-        <v>0.0009941760037643927</v>
+        <v>0.0008133507566344983</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.001089945894808281</v>
+        <v>0.001049978297409909</v>
       </c>
       <c r="R81" t="n">
-        <v>0.001625592331057221</v>
+        <v>0.001510232139712864</v>
       </c>
       <c r="S81" t="n">
-        <v>0.001064798044661318</v>
+        <v>0.4999999998124061</v>
       </c>
       <c r="T81" t="n">
-        <v>0.002827957156779928</v>
+        <v>0.002579667223187556</v>
       </c>
       <c r="U81" t="n">
-        <v>0.001928642980063544</v>
+        <v>0.001710566263336124</v>
       </c>
       <c r="V81" t="n">
-        <v>0.001972747734116421</v>
+        <v>0.001865962732696273</v>
       </c>
       <c r="W81" t="n">
-        <v>0.002556026783159283</v>
+        <v>0.002217389377482863</v>
       </c>
       <c r="X81" t="n">
-        <v>0.2400338486673622</v>
+        <v>19132.69564822977</v>
       </c>
     </row>
     <row r="82">
@@ -6965,67 +6965,67 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E82" t="n">
         <v>57.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3730456209331519</v>
+        <v>0.3730456210575596</v>
       </c>
       <c r="G82" t="n">
         <v>0.05530667551573475</v>
       </c>
       <c r="H82" t="n">
-        <v>0.261472183194441</v>
+        <v>0.2614721829646628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3101755203566725</v>
+        <v>0.3101755204620427</v>
       </c>
       <c r="J82" t="n">
-        <v>1.336850539002381e-17</v>
+        <v>8.893357462748227e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2412565016490764</v>
+        <v>0.1765487811080885</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1979729233005847</v>
+        <v>0.1552016382331313</v>
       </c>
       <c r="M82" t="n">
-        <v>4.565503289099579</v>
+        <v>4.560415235197789</v>
       </c>
       <c r="N82" t="n">
-        <v>4.582031148152657</v>
+        <v>4.558824721363435</v>
       </c>
       <c r="O82" t="n">
-        <v>0.001936031824944355</v>
+        <v>0.001870773686023851</v>
       </c>
       <c r="P82" t="n">
-        <v>0.0009338004885836286</v>
+        <v>0.0007934080260892822</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.001158881302568638</v>
+        <v>0.001092430407332025</v>
       </c>
       <c r="R82" t="n">
-        <v>0.00176346284477468</v>
+        <v>0.00165852764207381</v>
       </c>
       <c r="S82" t="n">
-        <v>1e-05</v>
+        <v>0.001271875756459855</v>
       </c>
       <c r="T82" t="n">
-        <v>0.00323522276109221</v>
+        <v>0.003012987970889347</v>
       </c>
       <c r="U82" t="n">
-        <v>0.00226302240339197</v>
+        <v>0.00265570233776024</v>
       </c>
       <c r="V82" t="n">
-        <v>0.002137749759046342</v>
+        <v>0.001971070476666519</v>
       </c>
       <c r="W82" t="n">
-        <v>0.002743753088870204</v>
+        <v>0.002546625601512968</v>
       </c>
       <c r="X82" t="n">
-        <v>0.1324111188190454</v>
+        <v>0.5231093392524148</v>
       </c>
     </row>
     <row r="83">
@@ -7045,65 +7045,65 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>0.3465778704093958</v>
+        <v>0.3465778699121797</v>
       </c>
       <c r="G83" t="n">
-        <v>0.07437667461883628</v>
+        <v>0.07437667876585422</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2955634795127128</v>
+        <v>0.2955634788718243</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2811992414815186</v>
+        <v>0.2811992393986867</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002282733977536599</v>
+        <v>0.002282733051455125</v>
       </c>
       <c r="K83" t="n">
-        <v>0.1893201329245792</v>
+        <v>0.07426204831243138</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1633878194827546</v>
+        <v>0.1248917168356015</v>
       </c>
       <c r="M83" t="n">
-        <v>4.564640100772776</v>
+        <v>2.766457713244925</v>
       </c>
       <c r="N83" t="n">
-        <v>4.536128350486222</v>
+        <v>4.535888262839383</v>
       </c>
       <c r="O83" t="n">
-        <v>0.001344664466691339</v>
+        <v>0.001283679550560779</v>
       </c>
       <c r="P83" t="n">
-        <v>0.0005232425800447533</v>
+        <v>0.0004169251349082251</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.0009109938766461207</v>
+        <v>0.0008945443600636554</v>
       </c>
       <c r="R83" t="n">
-        <v>0.00142691119175134</v>
+        <v>0.001319244345773764</v>
       </c>
       <c r="S83" t="n">
-        <v>0.003415240425167471</v>
+        <v>0.4999999920346217</v>
       </c>
       <c r="T83" t="n">
-        <v>0.002298300196210596</v>
+        <v>0.002448914008714605</v>
       </c>
       <c r="U83" t="n">
-        <v>0.001851707815071694</v>
+        <v>0.001492992733760166</v>
       </c>
       <c r="V83" t="n">
-        <v>0.001764819366793604</v>
+        <v>0.00166970417559479</v>
       </c>
       <c r="W83" t="n">
-        <v>0.00253536536286716</v>
+        <v>0.002310386307087481</v>
       </c>
       <c r="X83" t="n">
-        <v>1.273423385908582</v>
+        <v>3962.229458821069</v>
       </c>
     </row>
     <row r="84">
@@ -7123,65 +7123,65 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>0.4410213099976569</v>
+        <v>0.4410213107040933</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0196358885772423</v>
+        <v>0.01963588269307707</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3091324863805823</v>
+        <v>0.3091324872855457</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2286307167377633</v>
+        <v>0.2286307196912758</v>
       </c>
       <c r="J84" t="n">
-        <v>0.001579598306755124</v>
+        <v>0.001579599626008144</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1682613988596496</v>
+        <v>0.08086508415964506</v>
       </c>
       <c r="L84" t="n">
-        <v>0.2390626965961163</v>
+        <v>0.2380868656973389</v>
       </c>
       <c r="M84" t="n">
-        <v>4.508063032274873</v>
+        <v>3.412696456024068</v>
       </c>
       <c r="N84" t="n">
-        <v>4.520761102593896</v>
+        <v>4.470754793243954</v>
       </c>
       <c r="O84" t="n">
-        <v>0.001657356082844849</v>
+        <v>0.001522947964848235</v>
       </c>
       <c r="P84" t="n">
-        <v>1.000000000000001e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.001713721136949982</v>
+        <v>0.002077815319174143</v>
       </c>
       <c r="R84" t="n">
-        <v>0.001993276987733432</v>
+        <v>0.00188914137155105</v>
       </c>
       <c r="S84" t="n">
-        <v>1e-05</v>
+        <v>0.49999999979495</v>
       </c>
       <c r="T84" t="n">
-        <v>0.002618429908231946</v>
+        <v>0.002495852437407883</v>
       </c>
       <c r="U84" t="n">
-        <v>0.002574071079047076</v>
+        <v>0.003360385041311306</v>
       </c>
       <c r="V84" t="n">
-        <v>0.003104847822386465</v>
+        <v>0.006172978640632325</v>
       </c>
       <c r="W84" t="n">
-        <v>0.003208491857073132</v>
+        <v>0.004129747636430496</v>
       </c>
       <c r="X84" t="n">
-        <v>0.1142610765549325</v>
+        <v>7871.117820368519</v>
       </c>
     </row>
     <row r="85">
@@ -7201,65 +7201,67 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>46.1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0.5131512316840431</v>
+        <v>0.510053670891675</v>
       </c>
       <c r="G85" t="n">
-        <v>6.514458245503142e-16</v>
+        <v>0.06886340942740074</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2632803536988662</v>
+        <v>0.2213241491814443</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2235684146170903</v>
+        <v>0.19975877049948</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-17</v>
       </c>
       <c r="K85" t="n">
-        <v>0.2323848211746669</v>
+        <v>0.2340214112424731</v>
       </c>
       <c r="L85" t="n">
-        <v>0.2781537466741126</v>
+        <v>0.2154715704585184</v>
       </c>
       <c r="M85" t="n">
-        <v>4.457929099338116</v>
+        <v>4.336377550811515</v>
       </c>
       <c r="N85" t="n">
-        <v>4.497049858891337</v>
+        <v>4.41495720204485</v>
       </c>
       <c r="O85" t="n">
-        <v>0.001537878270432562</v>
+        <v>0.001753209427294152</v>
       </c>
       <c r="P85" t="n">
-        <v>1e-05</v>
+        <v>0.0007164008941041827</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.001458152609940719</v>
+        <v>0.001021581621834696</v>
       </c>
       <c r="R85" t="n">
-        <v>0.001725963154681303</v>
+        <v>0.001363252148446258</v>
       </c>
       <c r="S85" t="n">
-        <v>1.000000000000169e-05</v>
+        <v>1.000000000000017e-05</v>
       </c>
       <c r="T85" t="n">
-        <v>0.002395023589641333</v>
+        <v>0.002585375101555086</v>
       </c>
       <c r="U85" t="n">
-        <v>0.004200665074478106</v>
+        <v>0.001962821353709164</v>
       </c>
       <c r="V85" t="n">
-        <v>0.002753055618647909</v>
+        <v>0.001845846094770739</v>
       </c>
       <c r="W85" t="n">
-        <v>0.002670829493561966</v>
+        <v>0.002233063856194728</v>
       </c>
       <c r="X85" t="n">
-        <v>0.12322268633373</v>
+        <v>0.1569158915513229</v>
       </c>
     </row>
     <row r="86">
@@ -7279,65 +7281,67 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>21</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E86" t="n">
+        <v>45.1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0.3947553823403973</v>
+        <v>0.3945200239537214</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0245670665763035</v>
+        <v>0.07039031429275332</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3466305638791009</v>
+        <v>0.3115441195160394</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2327646937884924</v>
+        <v>0.2235455422374857</v>
       </c>
       <c r="J86" t="n">
-        <v>0.001282293415705915</v>
+        <v>4.155543639229597e-17</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1216797013469085</v>
+        <v>0.1048616824214853</v>
       </c>
       <c r="L86" t="n">
-        <v>0.5524543808934933</v>
+        <v>0.1405602909660879</v>
       </c>
       <c r="M86" t="n">
-        <v>4.463874829234726</v>
+        <v>4.456854714452565</v>
       </c>
       <c r="N86" t="n">
-        <v>4.582655327295303</v>
+        <v>4.450371510761645</v>
       </c>
       <c r="O86" t="n">
-        <v>0.002105778017488717</v>
+        <v>0.001580786395500973</v>
       </c>
       <c r="P86" t="n">
-        <v>0.001853286418637524</v>
+        <v>0.0007120261674759246</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.01638113508735727</v>
+        <v>0.001384692545194863</v>
       </c>
       <c r="R86" t="n">
-        <v>0.003749187766614423</v>
+        <v>0.001509622571136266</v>
       </c>
       <c r="S86" t="n">
-        <v>1.000001621581099e-05</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="T86" t="n">
-        <v>0.004030854014833741</v>
+        <v>0.002419921040134105</v>
       </c>
       <c r="U86" t="n">
-        <v>0.005097234427115398</v>
+        <v>0.001891364002040765</v>
       </c>
       <c r="V86" t="n">
-        <v>0.2988902284032829</v>
+        <v>0.002380792786045974</v>
       </c>
       <c r="W86" t="n">
-        <v>0.007289430432498077</v>
+        <v>0.002359953821203105</v>
       </c>
       <c r="X86" t="n">
-        <v>0.03590971658962546</v>
+        <v>30391.75781778825</v>
       </c>
     </row>
     <row r="87">
@@ -7357,65 +7361,67 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>21</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E87" t="n">
+        <v>57.4</v>
+      </c>
       <c r="F87" t="n">
-        <v>0.3717923415656336</v>
+        <v>0.3694757755244492</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.05530667551573475</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3014084132402625</v>
+        <v>0.2674527900009642</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3267992451941039</v>
+        <v>0.3077647589588519</v>
       </c>
       <c r="J87" t="n">
-        <v>1.327388309752159e-16</v>
+        <v>2.355429219724758e-17</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1836792903153103</v>
+        <v>0.1671203248578332</v>
       </c>
       <c r="L87" t="n">
-        <v>0.2895807275144486</v>
+        <v>0.1599259790535159</v>
       </c>
       <c r="M87" t="n">
-        <v>4.626284385528607</v>
+        <v>4.559806916648162</v>
       </c>
       <c r="N87" t="n">
-        <v>4.640016802743303</v>
+        <v>4.551763587317457</v>
       </c>
       <c r="O87" t="n">
-        <v>0.001943392693753494</v>
+        <v>0.002001173197883897</v>
       </c>
       <c r="P87" t="n">
-        <v>1e-05</v>
+        <v>0.0009940053700162178</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.002136666960040022</v>
+        <v>0.001296783586050699</v>
       </c>
       <c r="R87" t="n">
-        <v>0.002211464152663781</v>
+        <v>0.001813526080784904</v>
       </c>
       <c r="S87" t="n">
-        <v>1.000000000000003e-05</v>
+        <v>0.001599980806037339</v>
       </c>
       <c r="T87" t="n">
-        <v>0.003152051349673983</v>
+        <v>0.00323320998253343</v>
       </c>
       <c r="U87" t="n">
-        <v>0.004666912224248201</v>
+        <v>0.002701565673539168</v>
       </c>
       <c r="V87" t="n">
-        <v>0.004128716380401555</v>
+        <v>0.002331200760865423</v>
       </c>
       <c r="W87" t="n">
-        <v>0.003518399688525571</v>
+        <v>0.002791288692175516</v>
       </c>
       <c r="X87" t="n">
-        <v>0.114722663769622</v>
+        <v>0.6041946444845688</v>
       </c>
     </row>
     <row r="88">
@@ -7435,65 +7441,67 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>21</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E88" t="n">
+        <v>53.2</v>
+      </c>
       <c r="F88" t="n">
-        <v>0.3917057203335357</v>
+        <v>0.3890440313612025</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.05967299200381906</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2685425476164555</v>
+        <v>0.2320759063377122</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3397517320500086</v>
+        <v>0.3192070702972664</v>
       </c>
       <c r="J88" t="n">
-        <v>1.912261794240524e-16</v>
+        <v>2.419504177564497e-17</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2310798287540956</v>
+        <v>0.2271484743973362</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1753063908738903</v>
+        <v>0.2159963854830659</v>
       </c>
       <c r="M88" t="n">
-        <v>4.58573710713803</v>
+        <v>4.564427371312389</v>
       </c>
       <c r="N88" t="n">
-        <v>4.622456863247761</v>
+        <v>4.543502089107221</v>
       </c>
       <c r="O88" t="n">
-        <v>0.00160873111546925</v>
+        <v>0.001810430985681486</v>
       </c>
       <c r="P88" t="n">
-        <v>0.0001796900015768536</v>
+        <v>0.0009697573778730542</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.0008582861944874677</v>
+        <v>0.001141137013397845</v>
       </c>
       <c r="R88" t="n">
-        <v>0.001384085583171686</v>
+        <v>0.001661300457918476</v>
       </c>
       <c r="S88" t="n">
-        <v>1.000000000000001e-05</v>
+        <v>0.08271557547383473</v>
       </c>
       <c r="T88" t="n">
-        <v>0.002573234283933019</v>
+        <v>0.002750403320193811</v>
       </c>
       <c r="U88" t="n">
-        <v>0.003582093488002414</v>
+        <v>0.001686891595161994</v>
       </c>
       <c r="V88" t="n">
-        <v>0.0016059271903689</v>
+        <v>0.002010837826710848</v>
       </c>
       <c r="W88" t="n">
-        <v>0.00216424116800345</v>
+        <v>0.002434061972456028</v>
       </c>
       <c r="X88" t="n">
-        <v>0.1745611660210928</v>
+        <v>561.8925857523346</v>
       </c>
     </row>
     <row r="89">
@@ -7513,65 +7521,65 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>0.468689526729295</v>
+        <v>0.4686895267262085</v>
       </c>
       <c r="G89" t="n">
-        <v>3.650881409255485e-16</v>
+        <v>2.428629807026475e-16</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1956707823068736</v>
+        <v>0.1956707823126708</v>
       </c>
       <c r="I89" t="n">
-        <v>0.335639690963831</v>
+        <v>0.3356396909611205</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3492532603465395</v>
+        <v>0.2930745356554132</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3168784197576949</v>
+        <v>0.2724674106365489</v>
       </c>
       <c r="M89" t="n">
-        <v>4.506874220132712</v>
+        <v>4.501955864778384</v>
       </c>
       <c r="N89" t="n">
-        <v>4.605018665598963</v>
+        <v>4.555634811674868</v>
       </c>
       <c r="O89" t="n">
-        <v>0.002482369742675037</v>
+        <v>0.002329409442582674</v>
       </c>
       <c r="P89" t="n">
-        <v>0.0007937131076600682</v>
+        <v>0.0004171179778321169</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.001392508874952393</v>
+        <v>0.001380244353122946</v>
       </c>
       <c r="R89" t="n">
-        <v>0.001928392340120692</v>
+        <v>0.001785358381033958</v>
       </c>
       <c r="S89" t="n">
-        <v>1.000000000008575e-05</v>
+        <v>0.4999999999999996</v>
       </c>
       <c r="T89" t="n">
-        <v>0.004092766152377545</v>
+        <v>0.003758264680670564</v>
       </c>
       <c r="U89" t="n">
-        <v>0.003244482729960029</v>
+        <v>0.003277195292478167</v>
       </c>
       <c r="V89" t="n">
-        <v>0.002434802378624075</v>
+        <v>0.00243318191360753</v>
       </c>
       <c r="W89" t="n">
-        <v>0.002865009559323021</v>
+        <v>0.002596574911052883</v>
       </c>
       <c r="X89" t="n">
-        <v>0.07238274145998064</v>
+        <v>12535.56082441183</v>
       </c>
     </row>
     <row r="90">
@@ -7593,63 +7601,65 @@
       <c r="D90" t="n">
         <v>12.8</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>30.13605442176871</v>
+      </c>
       <c r="F90" t="n">
-        <v>0.6963378304438156</v>
+        <v>0.6739262842370797</v>
       </c>
       <c r="G90" t="n">
-        <v>0.06121827372612768</v>
+        <v>0.1053423626787058</v>
       </c>
       <c r="H90" t="n">
-        <v>0.04157121397092656</v>
+        <v>0.01105388716074765</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1708251520974169</v>
+        <v>0.1819763294359777</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03004752976171331</v>
+        <v>0.02770113648748916</v>
       </c>
       <c r="K90" t="n">
-        <v>0.5584612234091498</v>
+        <v>0.5772933408370901</v>
       </c>
       <c r="L90" t="n">
-        <v>0.5226634916738105</v>
+        <v>0.5405362122541715</v>
       </c>
       <c r="M90" t="n">
-        <v>4.519924070708985</v>
+        <v>4.576541863507602</v>
       </c>
       <c r="N90" t="n">
-        <v>4.27461395452075</v>
+        <v>4.294680282680988</v>
       </c>
       <c r="O90" t="n">
-        <v>0.004337955081436859</v>
+        <v>0.003790541690566715</v>
       </c>
       <c r="P90" t="n">
-        <v>0.003645648491050805</v>
+        <v>0.00455266658608908</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.008139724346394228</v>
+        <v>0.007212091918324338</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01264140839814257</v>
+        <v>0.01222583212808292</v>
       </c>
       <c r="S90" t="n">
-        <v>0.002956187110888113</v>
+        <v>0.002107518326910247</v>
       </c>
       <c r="T90" t="n">
-        <v>0.00906787016073482</v>
+        <v>0.006407544255252139</v>
       </c>
       <c r="U90" t="n">
-        <v>0.005840870347575667</v>
+        <v>0.005669760368756288</v>
       </c>
       <c r="V90" t="n">
-        <v>0.01353735078617368</v>
+        <v>0.006347246472998327</v>
       </c>
       <c r="W90" t="n">
-        <v>0.03259659205547456</v>
+        <v>0.03080754585152705</v>
       </c>
       <c r="X90" t="n">
-        <v>0.09127196668728899</v>
+        <v>0.05675941862314548</v>
       </c>
     </row>
   </sheetData>
